--- a/results/badanie_groupchat_wyniki.xlsx
+++ b/results/badanie_groupchat_wyniki.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wyniki_Zadan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Podsumowanie_Kategorii" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ewolucja_Tur" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statystyka_Naukowa" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wyniki_Szczegolowe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analiza_Kategorii" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analiza_Trudnosci" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ewolucja_Dyskusji" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statystyka_Akademicka" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,33 +436,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X3"/>
+  <dimension ref="A1:AE36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="25" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="33" customWidth="1" min="23" max="23"/>
-    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="25" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="15" customWidth="1" min="29" max="29"/>
+    <col width="33" customWidth="1" min="30" max="30"/>
+    <col width="24" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,110 +485,145 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>required_tool</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>score_solo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>score_multi_5</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>score_multi_10</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>score_multi_final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>debate_gain</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>gt_solo_score</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>gt_multi_score</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>hallucination_solo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hallucination_multi</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>solo_time</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>solo_generation_time</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>solo_tool_time</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>multi_time</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>multi_generation_time</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>multi_tool_time</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>solo_tokens</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>multi_tokens</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>solo_cost_usd</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>multi_cost_usd</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>solo_turns</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>multi_turns</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>solo_tools_used</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>multi_tools_used</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>multi_tool_errors</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>jury_std_dev</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>agent_path</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jury_reason</t>
         </is>
@@ -597,72 +640,97 @@
           <t>physics_commonsense</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>70</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="b">
+        <v>95</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="U2" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="V2" s="2" t="n">
         <v>0.0001</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="W2" s="2" t="n">
         <v>0.0004</v>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" s="2" t="n">
+      <c r="X2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>analyst -&gt; solver -&gt; secretary</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>[Mock Jury]: Poprawne</t>
         </is>
@@ -679,72 +747,3628 @@
           <t>math_probability</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>70</v>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2" t="b">
+        <v>95</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="U3" s="2" t="n">
         <v>300</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="V3" s="2" t="n">
         <v>0.0001</v>
       </c>
-      <c r="T3" s="2" t="n">
+      <c r="W3" s="2" t="n">
         <v>0.0004</v>
       </c>
-      <c r="U3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="n">
+      <c r="X3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="Z3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>analyst -&gt; solver -&gt; secretary</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>task_03_fibonacci_sum</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>task_04_collatz_conjecture</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>task_05_strawberry</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>task_06_relativity</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>physics_commonsense</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>task_07_code_injection</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>coding_logic</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>task_08_probability_boy</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>math_probability</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>task_09_logic_grid</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>pure_logic</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>task_10_trick_math</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>physics_commonsense</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>task_11_log_parsing</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>sysadmin_security</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>task_12_subnetting</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>sysadmin_security</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>task_13_10000th_prime</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>task_14_crypto_base64_xor</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>cryptography_coding</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W15" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>task_15_cve_osint</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>web_osint</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>task_16_obfuscated_code</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>cryptography_coding</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>task_17_cron_logic</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>sysadmin_security</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W18" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>task_18_json_data_extraction</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>coding_analytics</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W19" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>task_19_graph_routing</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>algorithms_graph</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W20" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>task_20_vigenere_crypto</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>cryptography_coding</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W21" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>task_21_complex_compound_interest</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>coding_analytics</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>task_22_regex_ipv4_validation</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>coding_logic</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>task_23_anagram_groups</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>coding_analytics</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W24" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>task_24_noise_data_sanitization</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>coding_logic</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W25" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>task_25_perfect_numbers</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W26" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>task_26_sundays_20th_century</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>coding_analytics</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W27" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>task_27_fsharp_minor_frequencies</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>task_28_local_finance_margin</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>rag_local_docs</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>local_doc</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>task_29_local_incident_response</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>rag_local_docs</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>local_doc</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W30" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>task_30_local_project_gamma_access</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>rag_local_docs</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>local_doc</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>task_31_osint_heartbleed_cve</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>web_osint</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>task_32_knapsack_optimization</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>algorithms_graph</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>task_33_jwt_token_decoding</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>sysadmin_security</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>task_34_monte_carlo_pi</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>math_probability</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>[Mock Jury]: Poprawne</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>task_35_sql_injection_defense</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>appsec_code_review</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>analyst -&gt; solver -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
         <is>
           <t>[Mock Jury]: Poprawne</t>
         </is>
@@ -761,7 +4385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -772,6 +4396,7 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -815,15 +4440,20 @@
           <t>Multi_Koszt_USD</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Przewaga_Multi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>math_probability</t>
+          <t>algorithms_graph</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>80</v>
@@ -842,34 +4472,350 @@
       </c>
       <c r="H2" s="2" t="n">
         <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>appsec_code_review</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>coding_analytics</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>coding_logic</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>cryptography_coding</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>math_probability</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>physics_commonsense</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
+      <c r="B9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>pure_logic</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>rag_local_docs</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>sysadmin_security</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>web_osint</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -883,79 +4829,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>task_id</t>
+          <t>difficulty</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Solo_ReAct</t>
+          <t>Liczba_Zadan</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Multi_Tura_5</t>
+          <t>Solo_Średnia</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Multi_Tura_10</t>
+          <t>Multi_Średnia</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Multi_Finał</t>
+          <t>Solo_Czas_s</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Multi_Czas_s</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Solo_Tokeny</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Multi_Tokeny</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Przewaga_Multi</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>task_01_helium</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>95</v>
+        <v>0.1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>task_02_monty_hall_100</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>95</v>
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -969,7 +4994,831 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>task_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Solo_ReAct</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Multi_Tura_5</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Multi_Tura_10</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Multi_Finał</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Zysk_z_Dyskusji</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>task_01_helium</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>task_02_monty_hall_100</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>task_03_fibonacci_sum</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>task_04_collatz_conjecture</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>task_05_strawberry</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>task_06_relativity</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>task_07_code_injection</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>task_08_probability_boy</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>task_09_logic_grid</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>task_10_trick_math</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>task_11_log_parsing</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>task_12_subnetting</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>task_13_10000th_prime</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>task_14_crypto_base64_xor</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>task_15_cve_osint</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>task_16_obfuscated_code</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>task_17_cron_logic</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>task_18_json_data_extraction</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>task_19_graph_routing</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>task_20_vigenere_crypto</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>task_21_complex_compound_interest</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>task_22_regex_ipv4_validation</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>task_23_anagram_groups</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>task_24_noise_data_sanitization</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>task_25_perfect_numbers</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>task_26_sundays_20th_century</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>task_27_fsharp_minor_frequencies</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>task_28_local_finance_margin</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>task_29_local_incident_response</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>task_30_local_project_gamma_access</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>task_31_osint_heartbleed_cve</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>task_32_knapsack_optimization</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>task_33_jwt_token_decoding</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>task_34_monte_carlo_pi</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>task_35_sql_injection_defense</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -991,11 +5840,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Liczba zbadanych zadań</t>
+          <t>Liczba zbadanych zadań (N)</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -1061,7 +5910,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Różnica średnich (Delta)</t>
+          <t>Różnica średnich punktów (Delta)</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1071,27 +5920,27 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Zwycięstwa Multi-Agent</t>
+          <t>Rozmiar efektu (Cohen's d)</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Remisy</t>
+          <t>Zwycięstwa Multi-Agent</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Porażki Multi-Agent</t>
+          <t>Remisy</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1101,44 +5950,72 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Win Rate Multi-Agent (%)</t>
+          <t>Porażki Multi-Agent</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Test t-Studenta (p-value)</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr"/>
+          <t>Wskaźnik zwycięstw Multi-Agent (%)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Test t Istotny statystycznie (p &lt; 0.05)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr"/>
+          <t>Test t-Studenta sparowany (p-value)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Test Wilcoxona (p-value)</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr"/>
+          <t>Test t Istotny statystycznie (p &lt; 0.05)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Test Wilcoxona rang (p-value)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Wilcoxon Istotny statystycznie (p &lt; 0.05)</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Średnie odchylenie sędziów (Jury Std Dev)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2.5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/badanie_groupchat_wyniki.xlsx
+++ b/results/badanie_groupchat_wyniki.xlsx
@@ -436,10 +436,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -461,15 +461,18 @@
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="23" customWidth="1" min="23" max="23"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="15" customWidth="1" min="29" max="29"/>
-    <col width="118" customWidth="1" min="30" max="30"/>
-    <col width="737" customWidth="1" min="31" max="31"/>
+    <col width="91" customWidth="1" min="30" max="30"/>
+    <col width="104" customWidth="1" min="31" max="31"/>
+    <col width="35" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -628,6 +631,21 @@
           <t>jury_reason</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>failure_taxonomy</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>gpu_vram_mb</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>gpu_util_pct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -651,22 +669,22 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>91.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>100</v>
+        <v>77.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>100</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100</v>
@@ -678,62 +696,4085 @@
         <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>20.44</v>
+        <v>21.97</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>20.44</v>
+        <v>19.77</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>148.73</v>
+        <v>116.47</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>148.73</v>
+        <v>99</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0</v>
+        <v>17.47</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>798</v>
+        <v>1830</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>16949</v>
+        <v>19282</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0.00275</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>0.03192</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="n">
+        <v>6110</v>
+      </c>
+      <c r="AH2" s="2" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>task_02_monty_hall_100</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>math_probability</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>2003</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>15796</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>0.02669</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD3" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="n">
+        <v>4412</v>
+      </c>
+      <c r="AH3" s="2" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>task_03_fibonacci_sum</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>1232</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>17586</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0.00185</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>0.02938</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="n">
+        <v>4576</v>
+      </c>
+      <c r="AH4" s="2" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>task_04_collatz_conjecture</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>151.52</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>128.79</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>1755</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>21202</v>
+      </c>
+      <c r="V5" s="2" t="n">
+        <v>0.00263</v>
+      </c>
+      <c r="W5" s="2" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF5" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG5" s="2" t="n">
+        <v>4520</v>
+      </c>
+      <c r="AH5" s="2" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>task_05_strawberry</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>122.54</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>104.16</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>1535</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>23379</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0.03807</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF6" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG6" s="2" t="n">
+        <v>6155</v>
+      </c>
+      <c r="AH6" s="2" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>task_06_relativity</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>physics_commonsense</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>146.43</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>124.47</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>1942</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>20515</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>0.00291</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0.03377</v>
+      </c>
+      <c r="X7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD7" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF7" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG7" s="2" t="n">
+        <v>6088</v>
+      </c>
+      <c r="AH7" s="2" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>task_07_code_injection</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>coding_logic</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>97.63</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>82.98999999999999</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>1248</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>8723</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0.00187</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0.01608</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF8" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG8" s="2" t="n">
+        <v>4849</v>
+      </c>
+      <c r="AH8" s="2" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>task_08_probability_boy</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>math_probability</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>143.51</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>121.98</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>21.53</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>2130</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>10295</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>0.00319</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>0.01844</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF9" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG9" s="2" t="n">
+        <v>4440</v>
+      </c>
+      <c r="AH9" s="2" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>task_09_logic_grid</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>pure_logic</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>53.38</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>1331</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>15770</v>
+      </c>
+      <c r="V10" s="2" t="n">
         <v>0.002</v>
       </c>
-      <c r="W2" s="2" t="n">
-        <v>0.0309955</v>
-      </c>
-      <c r="X2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="2" t="n">
+      <c r="W10" s="2" t="n">
+        <v>0.02665</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF10" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG10" s="2" t="n">
+        <v>6115</v>
+      </c>
+      <c r="AH10" s="2" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>task_10_trick_math</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>physics_commonsense</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>63.41</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>1969</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>9935</v>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>0.00295</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD11" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF11" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG11" s="2" t="n">
+        <v>5787</v>
+      </c>
+      <c r="AH11" s="2" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>task_11_log_parsing</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>sysadmin_security</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>140.89</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>119.76</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>705</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>17080</v>
+      </c>
+      <c r="V12" s="2" t="n">
+        <v>0.00106</v>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>0.02862</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF12" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG12" s="2" t="n">
+        <v>5442</v>
+      </c>
+      <c r="AH12" s="2" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>task_12_subnetting</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>sysadmin_security</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>96.05</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>915</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>12282</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>0.00137</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>0.02142</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y13" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="Z2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; fact_checker -&gt; solver -&gt; devil -&gt; fact_checker -&gt; solver -&gt; critic -&gt; secretary</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>[phi4:latest]: Wszystkie odpowiedzi (A, B, C i D) są zgodne z poprawnym fizycznym wyjaśnieniem dotyczącym zachowania się balonu z hellem w przyspieszającym samochodzie. Każda odpowiedź poprawnie opisuje, że balon skieruje się do przodu ze względu na gradient ciśnień powstały przez ruch powietrza w kierunku tylnym podczas przyspieszenia. Wyjaśnienia są zgodne z fizycznymi prawami i nie zawierają błędów logicznych ani halucynacji. | [qwen2.5:14b]: Wszystkie odpowiedzi są zgodne z fizycznymi prawami i poprawnie wyjaśniają, dlaczego balon z helkiem unosi się ku przedniej części kabiny samochodu podczas przyspieszania. | [mistral-nemo:12b]: Odpowiedzi są poprawne i uzasadnione, ale odpowiedź A jest mniej precyzyjna niż pozostałe.</t>
-        </is>
+      <c r="Z13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF13" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG13" s="2" t="n">
+        <v>5734</v>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>task_13_10000th_prime</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>56.68</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>1912</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>6170</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>0.00287</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>0.01225</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="n">
+        <v>4664</v>
+      </c>
+      <c r="AH14" s="2" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>task_14_crypto_base64_xor</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>cryptography_coding</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>65.09</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>55.33</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>1304</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>20701</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>0.00196</v>
+      </c>
+      <c r="W15" s="2" t="n">
+        <v>0.03405</v>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="n">
+        <v>4824</v>
+      </c>
+      <c r="AH15" s="2" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>task_15_cve_osint</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>web_osint</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>60.86</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>1038</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>8551</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>0.00156</v>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>0.01583</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="n">
+        <v>4847</v>
+      </c>
+      <c r="AH16" s="2" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>task_16_obfuscated_code</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>cryptography_coding</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>65.66</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>2066</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>12526</v>
+      </c>
+      <c r="V17" s="2" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v>0.02179</v>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD17" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF17" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG17" s="2" t="n">
+        <v>4515</v>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>task_17_cron_logic</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>sysadmin_security</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>20.54</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>117.46</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>99.84</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>1922</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>22101</v>
+      </c>
+      <c r="V18" s="2" t="n">
+        <v>0.00288</v>
+      </c>
+      <c r="W18" s="2" t="n">
+        <v>0.03615</v>
+      </c>
+      <c r="X18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD18" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF18" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG18" s="2" t="n">
+        <v>5149</v>
+      </c>
+      <c r="AH18" s="2" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>task_18_json_data_extraction</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>coding_analytics</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>47.64</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>1081</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>9531</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>0.00162</v>
+      </c>
+      <c r="W19" s="2" t="n">
+        <v>0.0173</v>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF19" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG19" s="2" t="n">
+        <v>5967</v>
+      </c>
+      <c r="AH19" s="2" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>task_19_graph_routing</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>algorithms_graph</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>157.6</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>133.96</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>1472</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>9413</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>0.00221</v>
+      </c>
+      <c r="W20" s="2" t="n">
+        <v>0.01712</v>
+      </c>
+      <c r="X20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD20" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF20" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG20" s="2" t="n">
+        <v>5559</v>
+      </c>
+      <c r="AH20" s="2" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>task_20_vigenere_crypto</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>cryptography_coding</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>79.15000000000001</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>67.28</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>19152</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>0.00127</v>
+      </c>
+      <c r="W21" s="2" t="n">
+        <v>0.03173</v>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF21" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG21" s="2" t="n">
+        <v>4329</v>
+      </c>
+      <c r="AH21" s="2" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>task_21_complex_compound_interest</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>coding_analytics</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>79.76000000000001</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>1943</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>19418</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>0.00291</v>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>0.03213</v>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF22" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG22" s="2" t="n">
+        <v>4999</v>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>task_22_regex_ipv4_validation</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>coding_logic</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>60.56</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>902</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>6043</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>0.00135</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>0.01206</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF23" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG23" s="2" t="n">
+        <v>4466</v>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>task_23_anagram_groups</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>coding_analytics</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>130.46</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>110.89</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>2145</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>7343</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0.00322</v>
+      </c>
+      <c r="W24" s="2" t="n">
+        <v>0.01401</v>
+      </c>
+      <c r="X24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y24" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF24" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG24" s="2" t="n">
+        <v>5008</v>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>task_24_noise_data_sanitization</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>coding_logic</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>20.83</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>109.58</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>93.14</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>1076</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>14536</v>
+      </c>
+      <c r="V25" s="2" t="n">
+        <v>0.00161</v>
+      </c>
+      <c r="W25" s="2" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF25" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG25" s="2" t="n">
+        <v>5974</v>
+      </c>
+      <c r="AH25" s="2" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>task_25_perfect_numbers</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>147.79</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>125.62</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>1592</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>17114</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="W26" s="2" t="n">
+        <v>0.02867</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y26" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF26" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG26" s="2" t="n">
+        <v>4444</v>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>task_26_sundays_20th_century</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>coding_analytics</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>111.97</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>95.17</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>6962</v>
+      </c>
+      <c r="V27" s="2" t="n">
+        <v>0.00304</v>
+      </c>
+      <c r="W27" s="2" t="n">
+        <v>0.01344</v>
+      </c>
+      <c r="X27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF27" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG27" s="2" t="n">
+        <v>4747</v>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>task_27_fsharp_minor_frequencies</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>135.53</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>1956</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>10815</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>0.00293</v>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>0.01922</v>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y28" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF28" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG28" s="2" t="n">
+        <v>4872</v>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>task_28_local_finance_margin</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>rag_local_docs</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>local_doc</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>48.39</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>1657</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>15811</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>0.00249</v>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>0.02672</v>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF29" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG29" s="2" t="n">
+        <v>4108</v>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>task_29_local_incident_response</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>rag_local_docs</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>local_doc</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>100.72</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>1268</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>7896</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="W30" s="2" t="n">
+        <v>0.01484</v>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF30" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG30" s="2" t="n">
+        <v>6142</v>
+      </c>
+      <c r="AH30" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>task_30_local_project_gamma_access</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>rag_local_docs</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>local_doc</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>157.18</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>133.6</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>2195</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>21714</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>0.00329</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>0.03557</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF31" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG31" s="2" t="n">
+        <v>5431</v>
+      </c>
+      <c r="AH31" s="2" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>task_31_osint_heartbleed_cve</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>web_osint</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>web_search</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>961</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>20671</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>0.00144</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>0.03401</v>
+      </c>
+      <c r="X32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF32" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG32" s="2" t="n">
+        <v>5534</v>
+      </c>
+      <c r="AH32" s="2" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>task_32_knapsack_optimization</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>algorithms_graph</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>75.78</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>64.41</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>1483</v>
+      </c>
+      <c r="U33" s="2" t="n">
+        <v>9361</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>0.00222</v>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>0.01704</v>
+      </c>
+      <c r="X33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y33" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF33" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG33" s="2" t="n">
+        <v>5198</v>
+      </c>
+      <c r="AH33" s="2" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>task_33_jwt_token_decoding</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>sysadmin_security</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>1418</v>
+      </c>
+      <c r="U34" s="2" t="n">
+        <v>16286</v>
+      </c>
+      <c r="V34" s="2" t="n">
+        <v>0.00213</v>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>0.02743</v>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y34" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF34" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG34" s="2" t="n">
+        <v>4959</v>
+      </c>
+      <c r="AH34" s="2" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>task_34_monte_carlo_pi</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>math_probability</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>1116</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>19086</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>0.00167</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>0.03163</v>
+      </c>
+      <c r="X35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF35" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG35" s="2" t="n">
+        <v>4253</v>
+      </c>
+      <c r="AH35" s="2" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>task_35_sql_injection_defense</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>appsec_code_review</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>python</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>117.47</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>1875</v>
+      </c>
+      <c r="U36" s="2" t="n">
+        <v>8088</v>
+      </c>
+      <c r="V36" s="2" t="n">
+        <v>0.00281</v>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>0.01513</v>
+      </c>
+      <c r="X36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+        </is>
+      </c>
+      <c r="AF36" s="2" t="inlineStr">
+        <is>
+          <t>Brak Błędu (Sukces Merytoryczny)</t>
+        </is>
+      </c>
+      <c r="AG36" s="2" t="n">
+        <v>4738</v>
+      </c>
+      <c r="AH36" s="2" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -747,7 +4788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -811,32 +4852,373 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>algorithms_graph</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>116.69</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>25.65</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>appsec_code_review</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>117.47</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>coding_analytics</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>69.58</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>92.45999999999999</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>20.77</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>coding_logic</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>76.67</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>95.43000000000001</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>92.81999999999999</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>18.76</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>coding_math</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>62.23</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>89.81999999999999</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>111.98</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>27.59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>cryptography_coding</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>71.87</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>73.83</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>math_probability</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>65.03</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>89.53</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>101.64</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>physics_commonsense</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>20.44</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>148.73</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="2" t="n">
+      <c r="B9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>77.93000000000001</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>94.43000000000001</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>108.77</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
         <v>0.03</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>8.300000000000001</v>
+      <c r="I9" s="2" t="n">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>pure_logic</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>rag_local_docs</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>71.13</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>96.06999999999999</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>24.94</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>sysadmin_security</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>104.71</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>24.58</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>web_osint</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>10.95</v>
       </c>
     </row>
   </sheetData>
@@ -850,7 +5232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -918,28 +5300,90 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>91.7</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>20.44</v>
+        <v>14.98</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>148.73</v>
+        <v>93.09</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>798</v>
+        <v>1499.9</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>16949</v>
+        <v>14884.8</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>60.45</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>17.38</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>121.33</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>1647.62</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>14596.25</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>26.75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>65.64</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>91.14</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1510.06</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>13853.88</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>25.88</v>
       </c>
     </row>
   </sheetData>
@@ -953,10 +5397,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -1003,19 +5447,767 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>task_02_monty_hall_100</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>task_03_fibonacci_sum</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>task_04_collatz_conjecture</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>task_05_strawberry</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>task_06_relativity</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>task_07_code_injection</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>task_08_probability_boy</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>task_09_logic_grid</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>task_10_trick_math</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>task_11_log_parsing</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>task_12_subnetting</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>task_13_10000th_prime</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>task_14_crypto_base64_xor</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>task_15_cve_osint</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>task_16_obfuscated_code</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>task_17_cron_logic</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>task_18_json_data_extraction</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>task_19_graph_routing</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>task_20_vigenere_crypto</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>task_21_complex_compound_interest</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>task_22_regex_ipv4_validation</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>task_23_anagram_groups</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="E24" s="2" t="n">
         <v>91.7</v>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0</v>
+      <c r="F24" s="2" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>task_24_noise_data_sanitization</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>task_25_perfect_numbers</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>task_26_sundays_20th_century</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>task_27_fsharp_minor_frequencies</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>task_28_local_finance_margin</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>task_29_local_incident_response</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>task_30_local_project_gamma_access</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>task_31_osint_heartbleed_cve</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>task_32_knapsack_optimization</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>20.9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>task_33_jwt_token_decoding</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>task_34_monte_carlo_pi</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>task_35_sql_injection_defense</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>14.3</v>
       </c>
     </row>
   </sheetData>
@@ -1055,7 +6247,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -1065,7 +6257,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>91.7</v>
+        <v>69.66</v>
       </c>
     </row>
     <row r="4">
@@ -1075,7 +6267,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="5">
@@ -1085,7 +6277,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>91.7</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1095,7 +6287,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>100</v>
+        <v>91.81</v>
       </c>
     </row>
     <row r="7">
@@ -1105,7 +6297,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="8">
@@ -1115,7 +6307,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
@@ -1125,7 +6317,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>22.16</v>
       </c>
     </row>
     <row r="10">
@@ -1134,7 +6326,9 @@
           <t>Rozmiar efektu (Cohen's d)</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="n">
+        <v>2.342</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1143,7 +6337,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -1182,7 +6376,9 @@
           <t>Test t-Studenta sparowany (p-value)</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1190,7 +6386,9 @@
           <t>Test t Istotny statystycznie (p &lt; 0.05)</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1198,7 +6396,9 @@
           <t>Test Wilcoxona rang (p-value)</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1206,7 +6406,9 @@
           <t>Wilcoxon Istotny statystycznie (p &lt; 0.05)</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1215,7 +6417,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
     </row>
   </sheetData>

--- a/results/badanie_groupchat_wyniki.xlsx
+++ b/results/badanie_groupchat_wyniki.xlsx
@@ -461,16 +461,16 @@
     <col width="14" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="25" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
     <col width="15" customWidth="1" min="29" max="29"/>
-    <col width="91" customWidth="1" min="30" max="30"/>
-    <col width="104" customWidth="1" min="31" max="31"/>
-    <col width="35" customWidth="1" min="32" max="32"/>
+    <col width="173" customWidth="1" min="30" max="30"/>
+    <col width="1092" customWidth="1" min="31" max="31"/>
+    <col width="59" customWidth="1" min="32" max="32"/>
     <col width="14" customWidth="1" min="33" max="33"/>
     <col width="15" customWidth="1" min="34" max="34"/>
   </cols>
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100</v>
@@ -696,40 +696,40 @@
         <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>21.97</v>
+        <v>20.44</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>19.77</v>
+        <v>20.44</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>116.47</v>
+        <v>148.73</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>99</v>
+        <v>148.73</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>17.47</v>
+        <v>0</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>1830</v>
+        <v>798</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>19282</v>
+        <v>16949</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.00275</v>
+        <v>0.002</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.03192</v>
+        <v>0.0309955</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>0</v>
@@ -741,29 +741,21 @@
         <v>0</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; fact_checker -&gt; solver -&gt; devil -&gt; fact_checker -&gt; solver -&gt; critic -&gt; secretary</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
-        </is>
-      </c>
-      <c r="AG2" s="2" t="n">
-        <v>6110</v>
-      </c>
-      <c r="AH2" s="2" t="n">
-        <v>82</v>
-      </c>
+          <t>[phi4:latest]: Wszystkie odpowiedzi (A, B, C i D) są zgodne z poprawnym fizycznym wyjaśnieniem dotyczącym zachowania się balonu z hellem w przyspieszającym samochodzie. Każda odpowiedź poprawnie opisuje, że balon skieruje się do przodu ze względu na gradient ciśnień powstały przez ruch powietrza w kierunku tylnym podczas przyspieszenia. Wyjaśnienia są zgodne z fizycznymi prawami i nie zawierają błędów logicznych ani halucynacji. | [qwen2.5:14b]: Wszystkie odpowiedzi są zgodne z fizycznymi prawami i poprawnie wyjaśniają, dlaczego balon z helkiem unosi się ku przedniej części kabiny samochodu podczas przyspieszania. | [mistral-nemo:12b]: Odpowiedzi są poprawne i uzasadnione, ale odpowiedź A jest mniej precyzyjna niż pozostałe.</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AG2" s="2" t="inlineStr"/>
+      <c r="AH2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -787,100 +779,100 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>88.7</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>23.7</v>
+        <v>25</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>6.7</v>
+        <v>0.1</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>6.03</v>
+        <v>0.1</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>101.38</v>
+        <v>0.2</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>86.17</v>
+        <v>0.2</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>15.21</v>
+        <v>0</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>2003</v>
+        <v>100</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>15796</v>
+        <v>300</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.003</v>
+        <v>0.0001</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.02669</v>
+        <v>0.0004</v>
       </c>
       <c r="X3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>analyst -&gt; solver -&gt; secretary</t>
         </is>
       </c>
       <c r="AE3" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[Mock Jury]: Poprawne</t>
         </is>
       </c>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Kaskada Halucynacji (Cascading Hallucination)</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>4412</v>
+        <v>1655</v>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>91</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -905,100 +897,100 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>63.5</v>
+        <v>80</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>73.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>81.5</v>
+        <v>85</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="X4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>19.04</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>17.14</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>47.85</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>40.67</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>1232</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>17586</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>0.00185</v>
-      </c>
-      <c r="W4" s="2" t="n">
-        <v>0.02938</v>
-      </c>
-      <c r="X4" s="2" t="n">
+      <c r="Y4" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>11</v>
       </c>
       <c r="Z4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>analyst -&gt; solver -&gt; secretary</t>
         </is>
       </c>
       <c r="AE4" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[Mock Jury]: Poprawne</t>
         </is>
       </c>
       <c r="AF4" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Kaskada Halucynacji (Cascading Hallucination)</t>
         </is>
       </c>
       <c r="AG4" s="2" t="n">
-        <v>4576</v>
+        <v>1655</v>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>72</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -1023,88 +1015,88 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>55.2</v>
+        <v>75</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>82.8</v>
+        <v>98.3</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>88.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>100</v>
       </c>
       <c r="L5" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>21.28</v>
+        <v>33.56</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>19.15</v>
+        <v>33.48</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>2.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>151.52</v>
+        <v>401.99</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>128.79</v>
+        <v>400.6</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>22.73</v>
+        <v>1.39</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>1755</v>
+        <v>1790</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>21202</v>
+        <v>23964</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.00263</v>
+        <v>0.0045</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>0.0348</v>
+        <v>0.0615506</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y5" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="Z5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AB5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE5" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Modelu nie zawierała żadnego kodu ani szczegółów dotyczących procesu, co skutkowało brakiem precyzji i uzasadnienia. Zamiast tego, podał on tylko wynik, który był poprawny, ale bez dowodzenia poprawności. Odpowiedzi Multi-Agent były kompleksowe, zawierały kod oraz wyjaśnienie procesu, co zapewniało pełne zrozumienie i potwierdzenie poprawności wyniku. | [qwen2.5:14b]: Odpowiedź SOLO jest poprawna, ale brakuje szczegółowego uzasadnienia. Odpowiedzi MULTI-Agent są kompleksowe i zawierają szczegółowe analizy oraz potwierdzenie wyników. | [mistral-nemo:12b]: Odpowiedzi są zgodne z WZORCEM, uzasadnienie jest precyzyjne i poprawne.</t>
         </is>
       </c>
       <c r="AF5" s="2" t="inlineStr">
@@ -1113,10 +1105,10 @@
         </is>
       </c>
       <c r="AG5" s="2" t="n">
-        <v>4520</v>
+        <v>13724</v>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -1141,25 +1133,25 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>87.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>89.8</v>
+        <v>98.3</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="b">
         <v>0</v>
@@ -1168,73 +1160,73 @@
         <v>0</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>17.47</v>
+        <v>36.41</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>15.72</v>
+        <v>36.33</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>1.75</v>
+        <v>0.08</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>122.54</v>
+        <v>403.25</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>104.16</v>
+        <v>403.06</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>18.38</v>
+        <v>0.2</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>1535</v>
+        <v>1464</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>23379</v>
+        <v>24904</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>0.0023</v>
+        <v>0.0037</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>0.03807</v>
+        <v>0.0655824</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Modelu uzyskała wynik 362, co jest błędne. Przyczyną tego było prawdopodobnie niepoprawne obliczenie sumy w pierwszym wykonaniu kodu. Odpowiedzi Multi-Agent (Tura 5, Tura 10 i Finał) były poprawne zgodnie ze wzorcem, ponieważ wykryły wszystkie liczby pierwsze zawierające cyfrę '3' oraz obliczyły ich sumę jako 359. Solo Model halucynował wynik sumy. | [qwen2.5:14b]: Wynik solo jest prawidłowy, ale suma została obliczona niepoprawnie (362 zamiast 359). Wyniki multi-agentów są poprawne i zgodne ze wzorcem. | [mistral-nemo:12b]: Odpowiedź Solo Model - ReAct zawiera błąd w wyniku sumy liczb pierwszych, które zawierają cyfrę '3'. Poprawna suma to 304, a nie 362. Odpowiedzi Multi-Agent są poprawne i zgodne z WZORCEM.</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Przekroczenie Limitu Tur (No-Consensus Timeout)</t>
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>6155</v>
+        <v>13465</v>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>89</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -1259,67 +1251,67 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>67</v>
+        <v>33.3</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>78.3</v>
+        <v>83.3</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>83.2</v>
+        <v>86.7</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>88.8</v>
+        <v>91.7</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>100</v>
       </c>
       <c r="L7" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>7.08</v>
+        <v>23.11</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>6.37</v>
+        <v>23.11</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>146.43</v>
+        <v>319.4</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>124.47</v>
+        <v>319.4</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>21.96</v>
+        <v>0</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>1942</v>
+        <v>672</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>20515</v>
+        <v>24477</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.00291</v>
+        <v>0.0017</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.03377</v>
+        <v>0.0400079</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z7" s="2" t="n">
         <v>0</v>
@@ -1331,16 +1323,16 @@
         <v>0</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>1.2</v>
+        <v>11.79</v>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>fact_checker -&gt; solver -&gt; devil -&gt; fact_checker -&gt; solver -&gt; devil -&gt; fact_checker -&gt; solver -&gt; critic -&gt; secretary</t>
         </is>
       </c>
       <c r="AE7" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest błędna, ponieważ zakłada brak zmiany wagi pomimo anulowania efektu siły centrifugalnej przez ruch przeciwny do obrotu Ziemi. To prowadzi do niepoprawnego wniosku, że waga pozostaje taka sama. Z kolei odpowiedź Multi-Agent poprawnie wyjaśnia, jak zmniejszenie prędkości względem centrum Ziemi zwiększa wagę przez redukcję siły centrifugalnej, co jest zgodne z WZORCEM. | [qwen2.5:14b]: Wersja Solo zawiera błędy w interpretacji sił centrifugowych i ich wpływu na wagę. Wersje Multi-Agent poprawnie wyjaśniają, że biegnąc z prędkością obrotu Ziemi na równiku w kierunku zachodnim, zmniejsza się wpływ siły centrifugalnej, co prowadzi do wzrostu czujonej masy. | [mistral-nemo:12b]: Odpowiedź B i C są poprawne, ale odpowiedź A jest błędna. Odpowiedzi B i C mają poprawne uzasadnienie, jednak mają drobne nieścisłości w wyjaśnieniu przyczyny zmiany wagi.</t>
         </is>
       </c>
       <c r="AF7" s="2" t="inlineStr">
@@ -1349,10 +1341,10 @@
         </is>
       </c>
       <c r="AG7" s="2" t="n">
-        <v>6088</v>
+        <v>13600</v>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>74</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -1377,25 +1369,25 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>85.2</v>
+        <v>66.7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>13.2</v>
+        <v>100</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="L8" s="2" t="b">
         <v>0</v>
@@ -1404,73 +1396,73 @@
         <v>0</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>21.05</v>
+        <v>48.98</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>18.95</v>
+        <v>48.92</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>2.1</v>
+        <v>0.05</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>97.63</v>
+        <v>321</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>82.98999999999999</v>
+        <v>320.64</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>14.64</v>
+        <v>0.36</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>1248</v>
+        <v>2052</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>8723</v>
+        <v>21205</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>0.00187</v>
+        <v>0.0051</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>0.01608</v>
+        <v>0.0554011</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Z8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="AC8" s="2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE8" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest idealna, ponieważ poprawnie zidentyfikowała wynik i uzasadniła go w kontekście zadania. Odpowiedź Multi-Agent Tura 5 zawiera błąd wykonania, co skutkuje zerową oceną. W Tury 10 odpowiedź jest prawie idealna, ale brakuje wyraźnego kodu lub dowodu na poprawność wyniku. Finałowa odpowiedź Multi-Agent jest idealna, ponieważ zawiera zarówno poprawny wynik, jak i uzasadnienie zgodne z wymaganiami zadania. | [qwen2.5:14b]: Odpowiedź SOLO zawiera niepoprawne stwierdzenie o działaniu kodu bez pokazania go, co prowadzi do halucynacji. Odpowiedź MULTI-10 ma drobne nieścisłości w opisie (brak pokazywania kodu), ale wynik jest poprawny. Finalna odpowiedź MULTI jest idealna - pokazuje poprawny kod i uzasadnienie. | [mistral-nemo:12b]: Odpowiedź Solo jest częściowo poprawna, ponieważ uzasadnienie jest mało precyzyjne. Odpowiedzi Multi-Agent są idealne i zgodne z WZORCEM.</t>
         </is>
       </c>
       <c r="AF8" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Błąd Wykonania Kodu / Narzędzia (Tool Execution Failure)</t>
         </is>
       </c>
       <c r="AG8" s="2" t="n">
-        <v>4849</v>
+        <v>13602</v>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -1495,100 +1487,100 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>65.3</v>
+        <v>58.3</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>64.59999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>75.8</v>
+        <v>58.3</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>85.5</v>
+        <v>66.7</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>20.9</v>
+        <v>8.4</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>534.5</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>534.25</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>1150</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>31582</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>0.08371390000000001</v>
+      </c>
+      <c r="X9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>143.51</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>121.98</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>21.53</v>
-      </c>
-      <c r="T9" s="2" t="n">
-        <v>2130</v>
-      </c>
-      <c r="U9" s="2" t="n">
-        <v>10295</v>
-      </c>
-      <c r="V9" s="2" t="n">
-        <v>0.00319</v>
-      </c>
-      <c r="W9" s="2" t="n">
-        <v>0.01844</v>
-      </c>
-      <c r="X9" s="2" t="n">
+      <c r="Y9" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z9" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Y9" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z9" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA9" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>2.5</v>
+        <v>47.14</v>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE9" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest prawie poprawna, z uzasadnieniem logicznym i kodem, ale końcowy wynik nie zgadza się z WZORCEM. Ostateczny wynik w odpowiedzi Multi-Agent (Tura 10) jest błędny, ponieważ obliczenia są niepoprawne, a uzasadnienie opiera się na poprzednim błędnym wyniku. | [qwen2.5:14b]: Wariant odpowiedzi Solo zawiera błędy w obliczeniach i logice, podczas gdy multi-agent końcowy dostarcza poprawnego wyniku 5/14 z prawidłowym uzasadnieniem. | [mistral-nemo:12b]: Odpowiedź poprawna, zgodna z WZORCEM, uzasadnienie i dowód poprawny.</t>
         </is>
       </c>
       <c r="AF9" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Przekroczenie Limitu Tur (No-Consensus Timeout)</t>
         </is>
       </c>
       <c r="AG9" s="2" t="n">
-        <v>4440</v>
+        <v>13635</v>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>84</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -1613,25 +1605,25 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>74.8</v>
+        <v>41.7</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>68.7</v>
+        <v>83.3</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>85.5</v>
+        <v>83.3</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>26.1</v>
+        <v>16.7</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="b">
         <v>0</v>
@@ -1640,40 +1632,40 @@
         <v>0</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>19.76</v>
+        <v>25.72</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>17.78</v>
+        <v>25.72</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>62.8</v>
+        <v>296.91</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>53.38</v>
+        <v>296.91</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>9.42</v>
+        <v>0</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>1331</v>
+        <v>774</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>15770</v>
+        <v>16623</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>0.02665</v>
+        <v>0.0342317</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z10" s="2" t="n">
         <v>0</v>
@@ -1685,28 +1677,28 @@
         <v>0</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>solver -&gt; devil -&gt; solver -&gt; devil -&gt; solver -&gt; critic -&gt; secretary</t>
         </is>
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest błędna, ponieważ niepoprawnie wniosła, że Adam jest programistą. Analiza w Tury 5 poprawnie zidentyfikowała możliwe scenariusze i wykluczyła te prowadzące do sprzeczności, co doprowadziło do prawidłowego wniosku, że Adam jest testerem. Ostateczna odpowiedź Multi-Agent w Turze 10 poprawnie zidentyfikowała, że jedynym rozwiązaniem bez sprzeczności jest, gdy Adam jest testerem. | [qwen2.5:14b]: Odpowiedź w Multi-Agent - Finał jest zgodna z prawidłowym rozumowaniem i spełnia wszystkie warunki zadania. | [mistral-nemo:12b]: W odpowiedzi A, uzasadnienie jest poprawne, ale nie jest zupełnie precyzyjne. W odpowiedziach B, C i D, uzasadnienia są zupełnie poprawne i precyzyjne.</t>
         </is>
       </c>
       <c r="AF10" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Konformizm Grupowy / Brak Krytyki (Sycophancy)</t>
         </is>
       </c>
       <c r="AG10" s="2" t="n">
-        <v>6115</v>
+        <v>13635</v>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>89</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -1731,19 +1723,19 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>89.40000000000001</v>
+        <v>25</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>72</v>
+        <v>33.3</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>87.2</v>
+        <v>33.3</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>95.90000000000001</v>
+        <v>33.3</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>23.9</v>
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>100</v>
@@ -1752,79 +1744,79 @@
         <v>100</v>
       </c>
       <c r="L11" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>7.98</v>
+        <v>22.17</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>7.18</v>
+        <v>22.14</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>0.8</v>
+        <v>0.03</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>63.41</v>
+        <v>339.65</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>53.9</v>
+        <v>339.5</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>9.51</v>
+        <v>0.15</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>1969</v>
+        <v>676</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>9935</v>
+        <v>18827</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>0.00295</v>
+        <v>0.0017</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>0.0179</v>
+        <v>0.0496294</v>
       </c>
       <c r="X11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>1.6</v>
+        <v>47.14</v>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Wszystkie odpowiedzi błędnie interpretują zadanie, koncentrując się na obliczaniu objętości cylindra zamiast rozpoznawać, że w dziurze nie ma żadnej ziemi. Zgodnie ze WZORCEM, poprawna odpowiedź to 'None', ponieważ dziura jest pusta. | [qwen2.5:14b]: Wszystkie odpowiedzi obliczyły objętość worka, a nie skupiły się na tym, że w dziurze nie ma ziemi. | [mistral-nemo:12b]: Wynik poprawny, ale uzasadnienie mało precyzyjne lub drobne nieścisłości.</t>
         </is>
       </c>
       <c r="AF11" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Przekroczenie Limitu Tur (No-Consensus Timeout)</t>
         </is>
       </c>
       <c r="AG11" s="2" t="n">
-        <v>5787</v>
+        <v>13640</v>
       </c>
       <c r="AH11" s="2" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1849,22 +1841,22 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>75.2</v>
+        <v>83.3</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>72.8</v>
+        <v>91.7</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>85.2</v>
+        <v>100</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>12.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>100</v>
@@ -1876,61 +1868,61 @@
         <v>0</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>22.04</v>
+        <v>38.77</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>19.84</v>
+        <v>38.73</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>2.2</v>
+        <v>0.04</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>140.89</v>
+        <v>639.97</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>119.76</v>
+        <v>639.47</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>21.13</v>
+        <v>0.5</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>705</v>
+        <v>1149</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>17080</v>
+        <v>42733</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0.00106</v>
+        <v>0.0029</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.02862</v>
+        <v>0.1123529</v>
       </c>
       <c r="X12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE12" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo jest idealna, zgodnie z WZORCEM. Poprawnie używa regex i logiki czasowej do wyodrębnienia IP i obliczenia różnicy czasu. Odpowiedź Multi-Agent w Tury 5 jest poprawna, ale nieco mniej precyzyjna w prezentacji wyników. W Turze 10 wystąpił błąd wykonania z powodu problemu z zakresem zmiennej, co skutkowało oceną 25 pkt. Ostateczna odpowiedź Multi-Agent jest poprawna i zgodna z WZORCEM. | [qwen2.5:14b]: Multi-Agent (Tura 5) i Finał oferują poprawne rozwiązanie, które jest zgodne z wzorcem. Solo model ma nieco bardziej skomplikowany kod, ale uzyskuje prawidłowy wynik. Multi-Agent (Tura 10) początkowo miał problem z duplikatami, ale w finale został rozwiązany. | [mistral-nemo:12b]: Odpowiedź Solo jest częściowo poprawna, ponieważ zawiera błąd w uzasadnieniu. Odpowiedzi Multi-Agent są poprawne i zgodne z WZORCEM.</t>
         </is>
       </c>
       <c r="AF12" s="2" t="inlineStr">
@@ -1939,10 +1931,10 @@
         </is>
       </c>
       <c r="AG12" s="2" t="n">
-        <v>5442</v>
+        <v>13734</v>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -1967,88 +1959,88 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>62.6</v>
+        <v>83.3</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>79.5</v>
+        <v>100</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>27.4</v>
+        <v>41.7</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>100</v>
       </c>
       <c r="L13" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>20.59</v>
+        <v>30.17</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>18.53</v>
+        <v>30.11</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>2.06</v>
+        <v>0.06</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>113</v>
+        <v>374.27</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>96.05</v>
+        <v>373.95</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>16.95</v>
+        <v>0.32</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>915</v>
+        <v>1638</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>12282</v>
+        <v>23922</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>0.00137</v>
+        <v>0.0041</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>0.02142</v>
+        <v>0.063328</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AB13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" s="2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE13" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo (A) dostarcza poprawne wyniki, ale brakuje pełnego uzasadnienia i dowodu. Odpowiedź Multi-Agent Tura 5 zawiera błąd wykonania z powodu pominiętego importu, co skutkuje zerową oceną. Odpowiedzi Multi-Agent Tura 10 i Finał są poprawne, kompleksowe i dobrze uzasadnione, spełniając kryteria WZORCA. | [qwen2.5:14b]: Odpowiedź Solo jest poprawna i zgodna z WZORCEM, choć nie pokazano kodu. Multi-Agent w trzeciej turze poprawnie wykonał obliczenia i naprawił błąd importu biblioteki ipaddress. | [mistral-nemo:12b]: Odpowiedź Solo Model - ReAct jest częściowo poprawna, ale uzasadnienie mało precyzyjne. Odpowiedzi Multi-Agent są poprawne i zgodne z WZORCEM.</t>
         </is>
       </c>
       <c r="AF13" s="2" t="inlineStr">
@@ -2057,10 +2049,10 @@
         </is>
       </c>
       <c r="AG13" s="2" t="n">
-        <v>5734</v>
+        <v>13671</v>
       </c>
       <c r="AH13" s="2" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -2085,88 +2077,88 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>59.9</v>
+        <v>100</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>78.8</v>
+        <v>100</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>78.5</v>
+        <v>100</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>100</v>
       </c>
       <c r="L14" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>21.69</v>
+        <v>39.87</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>19.52</v>
+        <v>39.74</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>2.17</v>
+        <v>0.13</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>66.68000000000001</v>
+        <v>379.59</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>56.68</v>
+        <v>379.4</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>10</v>
+        <v>0.19</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>1912</v>
+        <v>958</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>6170</v>
+        <v>23165</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>0.00287</v>
+        <v>0.0024</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>0.01225</v>
+        <v>0.06162769999999999</v>
       </c>
       <c r="X14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE14" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Wszystkie odpowiedzi dostarczyły poprawny wynik, zgodnie z WZORCEM. Odpowiedź Solo Modelu użyła metody iteracyjnej do znajdowania 10,000-tej liczby pierwszej, co jest skuteczne i bezpośrednio odpowiada na zadanie. Multi-Agent odpowiedzi w różnych turach również poprawnie zaimplementowały Sieve of Eratosthenes i uzyskały poprawny wynik 104729. Brak halucynacji, ponieważ wszystkie odpowiedzi były dokładne i zgodne z WZORCEM. | [qwen2.5:14b]: Wszystkie odpowiedzi poprawnie obliczyły 10000-tą liczbę pierwszą jako 104729, bez halucynacji. | [mistral-nemo:12b]: Odpowiedzi są zgodne z WZORCEM i poprawnie uzasadnione.</t>
         </is>
       </c>
       <c r="AF14" s="2" t="inlineStr">
@@ -2175,10 +2167,10 @@
         </is>
       </c>
       <c r="AG14" s="2" t="n">
-        <v>4664</v>
+        <v>13671</v>
       </c>
       <c r="AH14" s="2" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -2203,100 +2195,100 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>71.5</v>
+        <v>41.7</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>67.8</v>
+        <v>33.3</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>81.3</v>
+        <v>41.7</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.1</v>
+        <v>66.7</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>11.84</v>
+        <v>46.54</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>10.66</v>
+        <v>46.38</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>1.18</v>
+        <v>0.16</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>65.09</v>
+        <v>954.84</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>55.33</v>
+        <v>953.85</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>9.76</v>
+        <v>0.99</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>1304</v>
+        <v>1078</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>20701</v>
+        <v>47086</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>0.00196</v>
+        <v>0.0027</v>
       </c>
       <c r="W15" s="2" t="n">
-        <v>0.03405</v>
+        <v>0.1220862</v>
       </c>
       <c r="X15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Y15" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AA15" s="2" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AB15" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC15" s="2" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE15" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo nie była zgodna z WZORCEM, ponieważ wyprodukowała ciąg znaków zawierający kontrolne znaki ASCII. Odpowiedź Multi-Agent w Turze 5 również nie spełniła oczekiwań, ponieważ nie dostarczyła poprawnego wyniku ani uzasadnienia. W Turze 10 zidentyfikowano błąd i podjęto kroki naprawcze, ale nadal nie osiągnięto ostatecznej poprawności. Ostatecznie w Finałowej odpowiedzi Multi-Agent dokonano poprawnego dekodowania Base64, wykonania operacji XOR z kluczem 42 i konwersji wyniku na ASCII, co doprowadziło do uzyskania poprawnego wyniku 'R?**+*+(.*', zgodnie z WZORCEM. | [qwen2.5:14b]: Wynik Solo nie jest zgodny z oczekiwaniami i zawiera błędy. Wyniki Multi-Agent są poprawne, ale w finale pokazano, że wynik może być inny niż oczekiwany ze względu na potencjalne problemy z środowiskiem lub implementacją. | [mistral-nemo:12b]: Odpowiedź Solo Model - ReAct jest częściowo poprawna, ale zawiera nieścisłości w uzasadnieniu. Odpowiedzi Multi-Agent są błędne, mimo że widać próbę poprawnego rozumowania. Odpowiedź Multi-Agent - Finał jest idealna i zgodna z WZORCEM.</t>
         </is>
       </c>
       <c r="AF15" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Przekroczenie Limitu Tur (No-Consensus Timeout)</t>
         </is>
       </c>
       <c r="AG15" s="2" t="n">
-        <v>4824</v>
+        <v>13667</v>
       </c>
       <c r="AH15" s="2" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -2321,100 +2313,100 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>85.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>76.7</v>
+        <v>33.3</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>90.3</v>
+        <v>33.3</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>95.2</v>
+        <v>33.3</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>100</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L16" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M16" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>20.78</v>
+        <v>26.04</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>18.7</v>
+        <v>22.22</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>2.08</v>
+        <v>3.82</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>47.79</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>60.86</v>
+        <v>46.7</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>10.74</v>
+        <v>1.08</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>1038</v>
+        <v>1401</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>8551</v>
+        <v>5759</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>0.00156</v>
+        <v>0.0035</v>
       </c>
       <c r="W16" s="2" t="n">
-        <v>0.01583</v>
+        <v>0.0131044</v>
       </c>
       <c r="X16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Y16" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="AB16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC16" s="2" t="n">
-        <v>2.5</v>
+        <v>47.14</v>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>analyst -&gt; solver -&gt; critic -&gt; secretary</t>
         </is>
       </c>
       <c r="AE16" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest dokładna, zgodnie z WZORCEM, podając CVSS v3.1 base score jako 10.0 i identyfikując Apache Log4j jako bibliotekę dotkniętą. Odpowiedzi Multi-Agent są niepoprawne, ponieważ podają błędny CVSS v3.1 base score jako 9.0, co stanowi halucynację w stosunku do WZORCA. | [qwen2.5:14b]: Odpowiedź SOLO jest prawidłowa, ale uzasadnienie nie jest doskonałe (CVSS wynosi 10.0 a nie 9.0). Odpowiedzi MULTI zawierają błędy informacje i halucynację. | [mistral-nemo:12b]: Odpowiedź Solo Model - ReAct jest częściowo błędna, ponieważ podaje błędną wersję Log4j, która jest wciąż podatna na atak. Odpowiedzi Multi-Agent są poprawne i zgodne z WZORCEM.</t>
         </is>
       </c>
       <c r="AF16" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Kaskada Halucynacji (Cascading Hallucination)</t>
         </is>
       </c>
       <c r="AG16" s="2" t="n">
-        <v>4847</v>
+        <v>13669</v>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2439,25 +2431,25 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>82</v>
+        <v>83.3</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>95.7</v>
+        <v>66.7</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>23.3</v>
+        <v>8.4</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>100</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="b">
         <v>0</v>
@@ -2466,73 +2458,73 @@
         <v>0</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>8.42</v>
+        <v>11.91</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>7.58</v>
+        <v>11.85</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>0.84</v>
+        <v>0.05</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>77.25</v>
+        <v>337.35</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>65.66</v>
+        <v>337.06</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>11.59</v>
+        <v>0.29</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>2066</v>
+        <v>1029</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>12526</v>
+        <v>21548</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>0.0031</v>
+        <v>0.0026</v>
       </c>
       <c r="W17" s="2" t="n">
-        <v>0.02179</v>
+        <v>0.0562671</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Z17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AB17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC17" s="2" t="n">
-        <v>2.6</v>
+        <v>47.14</v>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE17" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo jest idealna, zgodna z WZORCEM i poprawnie uzasadniona. Odpowiedzi Multi-Agent w Tury 5 miały drobne nieścisłości w wyniku (poprawny wynik to 'Walear', a nie 'Waleas'), ale późniejsze odpowiedzi były poprawne, zgodne z WZORCEM i dobrze uzasadnione. | [qwen2.5:14b]: Odpowiedź Solo jest częściowo poprawna, ale wynik 'Waleas' jest błędny. Wszystkie odpowiedzi Multi-Agent zawierają błędy i halucynacje w formie nieistniejącego ciągu znaków 'Walear'. | [mistral-nemo:12b]: Odpowiedź Solo Model - ReAct jest częściowo poprawna, ponieważ uzasadnienie jest nieścisłe. Odpowiedzi Multi-Agent są zgodne z WZORCEM i poprawnie uzasadnione.</t>
         </is>
       </c>
       <c r="AF17" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Przekroczenie Limitu Tur (No-Consensus Timeout)</t>
         </is>
       </c>
       <c r="AG17" s="2" t="n">
-        <v>4515</v>
+        <v>13667</v>
       </c>
       <c r="AH17" s="2" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2557,22 +2549,22 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>57.4</v>
+        <v>25</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>71.5</v>
+        <v>91.7</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>79.3</v>
+        <v>91.7</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>85.8</v>
+        <v>91.7</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>100</v>
@@ -2584,61 +2576,61 @@
         <v>0</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>20.54</v>
+        <v>16.01</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>18.49</v>
+        <v>16.01</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>117.46</v>
+        <v>175.94</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>99.84</v>
+        <v>175.94</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>17.62</v>
+        <v>0</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>1922</v>
+        <v>602</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>22101</v>
+        <v>11565</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>0.00288</v>
+        <v>0.0015</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>0.03615</v>
+        <v>0.0249682</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>1.1</v>
+        <v>11.79</v>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>solver -&gt; devil -&gt; solver -&gt; devil -&gt; solver -&gt; critic -&gt; secretary</t>
         </is>
       </c>
       <c r="AE18" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest niepoprawna, ponieważ błędnie zakłada, że CRON job nie będzie uruchamiany po godzinie 16:00 tego samego dnia. Zamiast tego, rozważa następny dzień (czwartek), pomijając nadchodzący czas wykonywania w tym samym dniu (środa, 16:15). Odpowiedzi Multi-Agent są poprawne i zgodne ze wzorcem, ponieważ dokładnie określają, że następny czas uruchomienia to środa, 16:15. Solo Model wykazuje halucynację, zakładając niepoprawną interpretację CRON job. | [qwen2.5:14b]: Odpowiedź SOLO jest błędna, ponieważ zignorowano możliwość wykonania zadania w tym samym dniu. Odpowiedzi MULTI-Agent są poprawne i zgodne ze wzorcem. | [mistral-nemo:12b]: Odpowiedź Solo Model - ReAct jest częściowo poprawna, ale błędnie interpretuje czas następnej wykonywanej pracy. Odpowiedzi Multi-Agent są poprawne i zgodne z WZORCEM.</t>
         </is>
       </c>
       <c r="AF18" s="2" t="inlineStr">
@@ -2647,10 +2639,10 @@
         </is>
       </c>
       <c r="AG18" s="2" t="n">
-        <v>5149</v>
+        <v>13671</v>
       </c>
       <c r="AH18" s="2" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -2675,22 +2667,22 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>75.3</v>
+        <v>83.3</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>94</v>
+        <v>98.3</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>92.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>100</v>
@@ -2702,61 +2694,61 @@
         <v>0</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>7.5</v>
+        <v>41.04</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>6.75</v>
+        <v>40.98</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>0.75</v>
+        <v>0.06</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>47.64</v>
+        <v>407.79</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>40.49</v>
+        <v>407.31</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>7.15</v>
+        <v>0.48</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>1081</v>
+        <v>2052</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>9531</v>
+        <v>26514</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>0.00162</v>
+        <v>0.0051</v>
       </c>
       <c r="W19" s="2" t="n">
-        <v>0.0173</v>
+        <v>0.06855799999999999</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Z19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA19" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="AB19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC19" s="2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE19" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Modelu jest zgodna z WZORCEM, poprawnie oblicza średni czas pracy dla każdego systemu operacyjnego. Odpowiedzi Multi-Agent w różnych turach również są poprawne i zgodne z WZORCEM, bez błędów logicznych ani halucynacji. Każda odpowiedź zawiera poprawną analizę i uzasadnienie. | [qwen2.5:14b]: Wyniki wieloagentowe są idealne, zgodnie z wzorcem. Wynik solo jest poprawny, ale brakuje szczegółowego uzasadnienia. | [mistral-nemo:12b]: Odpowiedź A jest częściowo poprawna, ale uzasadnienie mało precyzyjne. Odpowiedzi B i C są poprawne i zgodne z WZORCEM. Odpowiedź D jest idealna, zgodna z WZORCEM, poprawne uzasadnienie i dowód.</t>
         </is>
       </c>
       <c r="AF19" s="2" t="inlineStr">
@@ -2765,10 +2757,10 @@
         </is>
       </c>
       <c r="AG19" s="2" t="n">
-        <v>5967</v>
+        <v>13671</v>
       </c>
       <c r="AH19" s="2" t="n">
-        <v>83</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -2793,88 +2785,88 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>58.8</v>
+        <v>41.7</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>69.3</v>
+        <v>91.7</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>75.5</v>
+        <v>98.3</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>87.3</v>
+        <v>100</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>100</v>
       </c>
       <c r="L20" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>16.9</v>
+        <v>82.2</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>15.21</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>1.69</v>
+        <v>0.05</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>157.6</v>
+        <v>502.69</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>133.96</v>
+        <v>502.31</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>23.64</v>
+        <v>0.37</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>1472</v>
+        <v>3200</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>9413</v>
+        <v>32670</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>0.00221</v>
+        <v>0.008</v>
       </c>
       <c r="W20" s="2" t="n">
-        <v>0.01712</v>
+        <v>0.0858462</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y20" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA20" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AC20" s="2" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE20" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model zawiera błędne wyniki, ponieważ podaje niepoprawną ścieżkę (C -&gt; E -&gt; D -&gt; F) zamiast poprawnej (A -&gt; C -&gt; E -&gt; D -&gt; F). Brak jest również dowodu lub uzasadnienia dla tego wyniku. Odpowiedź Multi-Agent w Tury 5 dostarcza poprawnego kodu i wyjaśnia logikę, ale nie podaje ostatecznego wyniku. W Turze 10 Multi-Agent przedstawia kompleksowe rozwiązanie z poprawnymi wynikami, analizą i rekomendacjami, spełniającym kryteria wzorca. | [qwen2.5:14b]: Odpowiedź SOLO zawiera błędy w opisie ścieżki (zabrakło A), a także niepoprawnie obliczyła koszt. Odpowiedzi MULTI są poprawne, zgodne z WZORCEM i zawierają szczegółowe analizy. | [mistral-nemo:12b]: Odpowiedzi są zgodne z WZORCEM, poprawne uzasadnienie i dowód.</t>
         </is>
       </c>
       <c r="AF20" s="2" t="inlineStr">
@@ -2883,10 +2875,10 @@
         </is>
       </c>
       <c r="AG20" s="2" t="n">
-        <v>5559</v>
+        <v>13691</v>
       </c>
       <c r="AH20" s="2" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -2911,88 +2903,88 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>62.1</v>
+        <v>58.3</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>63.7</v>
+        <v>91.7</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>75.3</v>
+        <v>80</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>27.3</v>
+        <v>-16.7</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>100</v>
       </c>
       <c r="L21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>45.85</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>45.76</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>482.63</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>482.15</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>1060</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>20446</v>
+      </c>
+      <c r="V21" s="2" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="W21" s="2" t="n">
+        <v>0.0555887</v>
+      </c>
+      <c r="X21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N21" s="2" t="n">
-        <v>23.27</v>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>20.94</v>
-      </c>
-      <c r="P21" s="2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q21" s="2" t="n">
-        <v>79.15000000000001</v>
-      </c>
-      <c r="R21" s="2" t="n">
-        <v>67.28</v>
-      </c>
-      <c r="S21" s="2" t="n">
-        <v>11.87</v>
-      </c>
-      <c r="T21" s="2" t="n">
-        <v>850</v>
-      </c>
-      <c r="U21" s="2" t="n">
-        <v>19152</v>
-      </c>
-      <c r="V21" s="2" t="n">
-        <v>0.00127</v>
-      </c>
-      <c r="W21" s="2" t="n">
-        <v>0.03173</v>
-      </c>
-      <c r="X21" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="Y21" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z21" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA21" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AB21" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="AC21" s="2" t="n">
-        <v>1.2</v>
+        <v>35.36</v>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE21" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Modelu jest błędna, ponieważ zwraca 'HELLOWORLD' zamiast poprawnego wyniku 'SECURESYSTEM'. Wykazuje halucynację w rozwiązaniu. Odpowiedzi Multi-Agent są poprawne i zgodne z WZORCEM, co uzasadnia pełną ocenę. | [qwen2.5:14b]: Wynik w modelu Solo jest poprawny, ale uzasadnienie ma drobne nieścisłości. W modelach Multi-Agent wyniki są idealne i zgodne z wzorcem. | [mistral-nemo:12b]: Odpowiedź Solo Model - ReAct jest poprawna, ale zawiera błąd w kodzie. Odpowiedzi Multi-Agent są częściowo poprawne, jednak mają błędy w logice i uzasadnieniu.</t>
         </is>
       </c>
       <c r="AF21" s="2" t="inlineStr">
@@ -3001,10 +2993,10 @@
         </is>
       </c>
       <c r="AG21" s="2" t="n">
-        <v>4329</v>
+        <v>14067</v>
       </c>
       <c r="AH21" s="2" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22">
@@ -3029,25 +3021,25 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>76.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>24.3</v>
+        <v>41.7</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="b">
         <v>1</v>
@@ -3056,73 +3048,73 @@
         <v>0</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>16.95</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>15.25</v>
+        <v>87.98</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>1.7</v>
+        <v>0.09</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>79.76000000000001</v>
+        <v>647.28</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>67.8</v>
+        <v>646.98</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>11.96</v>
+        <v>0.3</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>1943</v>
+        <v>2202</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>19418</v>
+        <v>24430</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>0.00291</v>
+        <v>0.0055</v>
       </c>
       <c r="W22" s="2" t="n">
-        <v>0.03213</v>
+        <v>0.06364300000000001</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y22" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Z22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA22" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC22" s="2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE22" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest całkowicie niezgodna z poprawnym wynikiem, co wskazuje na halucynację. Odpowiedź Multi-Agent Tura 5 zawiera błędną logikę obliczeń, co skutkuje niewłaściwym wynikiem i uzasadnia ocenę 25 punktów. W Tury 10 poprawiono logikę, ale nadal nie osiągnięto dokładnego wyniku; jednakże uzasadnienie było bardziej precyzyjne, co uzasadnia 75 punktów. Ostateczna odpowiedź Multi-Agent jest zgodna z wzorcem i poprawnie uzasadniona, uzyskując pełną ocenę. | [qwen2.5:14b]: Wynik Solo jest błędny, wyniki Multi-Agent są poprawne i zgodne ze wzorcem. Wynik w Ture 5 ma drobne nieścisłości, ale w Finałowej turze jest idealny. | [mistral-nemo:12b]: Odpowiedź Solo Model - ReAct jest błędna, ale widać próbę poprawnego rozumowania. Odpowiedzi Multi-Agent dla tur 5, 10 i finałowa są zgodne z WZORCEM i poprawnie uzasadnione.</t>
         </is>
       </c>
       <c r="AF22" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Przekroczenie Limitu Tur (No-Consensus Timeout)</t>
         </is>
       </c>
       <c r="AG22" s="2" t="n">
-        <v>4999</v>
+        <v>14070</v>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
@@ -3147,100 +3139,100 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>59.6</v>
+        <v>75</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>86.59999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>92</v>
+        <v>96.7</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>26.6</v>
+        <v>20</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="L23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>118.53</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>118.35</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>2014.12</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>2012.34</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>1404</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>0.120549</v>
+      </c>
+      <c r="X23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="M23" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="2" t="n">
-        <v>22.06</v>
-      </c>
-      <c r="O23" s="2" t="n">
-        <v>19.85</v>
-      </c>
-      <c r="P23" s="2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q23" s="2" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="R23" s="2" t="n">
-        <v>60.56</v>
-      </c>
-      <c r="S23" s="2" t="n">
-        <v>10.69</v>
-      </c>
-      <c r="T23" s="2" t="n">
-        <v>902</v>
-      </c>
-      <c r="U23" s="2" t="n">
-        <v>6043</v>
-      </c>
-      <c r="V23" s="2" t="n">
-        <v>0.00135</v>
-      </c>
-      <c r="W23" s="2" t="n">
-        <v>0.01206</v>
-      </c>
-      <c r="X23" s="2" t="n">
+      <c r="Y23" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="Y23" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z23" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA23" s="2" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="AB23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC23" s="2" t="n">
-        <v>1</v>
+        <v>4.71</v>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE23" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Modelu dostarcza poprawny regex i skrypt, ale nie rozwiązuje problemu z dodatkowym niewłaściwym wynikiem '1.2.3.4'. Odpowiedź Multi-Agent Tura 5 identyfikuje ten błąd, ale nie zapewnia rozwiązania. W Tury 10 poprawiają regex i skrypt, aby wyeliminować niewłaściwe wyniki, co prowadzi do ostatecznego poprawnego wyniku w Finałowej odpowiedzi Multi-Agent. | [qwen2.5:14b]: Wszystkie odpowiedzi poprawnie rozwiązały zadanie, ale niektóre miały drobne nieścisłości w logice lub uzasadnieniu. | [mistral-nemo:12b]: Odpowiedź Solo Model - ReAct jest częściowo poprawna, ale uzasadnienie mało precyzyjne. Odpowiedź Multi-Agent - Tura 5 jest poprawna, natomiast odpowiedź Multi-Agent - Tura 10 jest błędna, choć widać próbę poprawnego rozumowania. Odpowiedź Multi-Agent - Finał jest poprawna.</t>
         </is>
       </c>
       <c r="AF23" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Przekroczenie Limitu Tur (No-Consensus Timeout)</t>
         </is>
       </c>
       <c r="AG23" s="2" t="n">
-        <v>4466</v>
+        <v>13776</v>
       </c>
       <c r="AH23" s="2" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
@@ -3265,22 +3257,22 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>68.8</v>
+        <v>83.3</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>74.8</v>
+        <v>100</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>89.5</v>
+        <v>100</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>16.9</v>
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>100</v>
@@ -3292,61 +3284,61 @@
         <v>0</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>17.58</v>
+        <v>39.46</v>
       </c>
       <c r="O24" s="2" t="n">
-        <v>15.82</v>
+        <v>39.4</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>1.76</v>
+        <v>0.06</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>130.46</v>
+        <v>269.39</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>110.89</v>
+        <v>269.15</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>19.57</v>
+        <v>0.24</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>2145</v>
+        <v>1869</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>7343</v>
+        <v>19751</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>0.00322</v>
+        <v>0.0047</v>
       </c>
       <c r="W24" s="2" t="n">
-        <v>0.01401</v>
+        <v>0.0516246</v>
       </c>
       <c r="X24" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Y24" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA24" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="Z24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="2" t="n">
+      <c r="AB24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AB24" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AC24" s="2" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE24" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest poprawna pod względem wyniku, ale brakuje szczegółowego uzasadnienia i analizy. Odpowiedzi Multi-Agent są kompleksowe, zawierają poprawny kod, jego wyjaśnienie oraz manualną weryfikację, co czyni je idealnymi zgodnie z WZORCEM. | [qwen2.5:14b]: Wszystkie odpowiedzi są zgodne ze wzorcem, poprawnie rozwiązały zadanie i nie zawierają błędów logiki lub halucynacji. | [mistral-nemo:12b]: Odpowiedź Solo Model - ReAct jest częściowo poprawna, ale uzasadnienie mało precyzyjne. Odpowiedzi Multi-Agent są zgodne z WZORCEM i poprawnie uzasadnione.</t>
         </is>
       </c>
       <c r="AF24" s="2" t="inlineStr">
@@ -3355,10 +3347,10 @@
         </is>
       </c>
       <c r="AG24" s="2" t="n">
-        <v>5008</v>
+        <v>13774</v>
       </c>
       <c r="AH24" s="2" t="n">
-        <v>88</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25">
@@ -3383,19 +3375,19 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>85.2</v>
+        <v>83.3</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>72.3</v>
+        <v>91.7</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>92.5</v>
+        <v>98.3</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>98.7</v>
+        <v>100</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>26.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>100</v>
@@ -3410,61 +3402,61 @@
         <v>0</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>23.14</v>
+        <v>29.93</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>20.83</v>
+        <v>29.88</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>2.31</v>
+        <v>0.05</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>109.58</v>
+        <v>451.72</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>93.14</v>
+        <v>451.43</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>16.44</v>
+        <v>0.29</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>1076</v>
+        <v>1722</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>14536</v>
+        <v>21371</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>0.00161</v>
+        <v>0.0043</v>
       </c>
       <c r="W25" s="2" t="n">
-        <v>0.0248</v>
+        <v>0.0558062</v>
       </c>
       <c r="X25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y25" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Z25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA25" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AB25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC25" s="2" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE25" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest idealna, zgodnie z WZORCEM. Obejmuje ona poprawne uzasadnienie i dowód, co przynosi pełną ocenę 100 pkt. Multi-Agent Tura 5 dostarcza poprawny wynik, ale brakuje precyzyjnego uzasadnienia, co prowadzi do oceny 75 pkt. Odpowiedź Multi-Agent Tura 10 jest idealna i zgodna z WZORCEM, co przynosi pełną ocenę 100 pkt. Podobnie, odpowiedź Multi-Agent Finał jest kompletna i poprawna, uzyskując pełną ocenę 100 pkt. Brak halucynacji w żadnej z odpowiedzi. | [qwen2.5:14b]: Wszystkie odpowiedzi zgodne z wzorcem, ale w przypadku ODPOWIEDZI A brakuje konkretnych obliczeń i pełnej analizy, co spowodowało odjęcie punktów. | [mistral-nemo:12b]: Odpowiedź A jest częściowo poprawna, ale uzasadnienie jest mało precyzyjne. Odpowiedzi B, C i D są zgodne z WZORCEM i poprawnie uzasadnione.</t>
         </is>
       </c>
       <c r="AF25" s="2" t="inlineStr">
@@ -3473,10 +3465,10 @@
         </is>
       </c>
       <c r="AG25" s="2" t="n">
-        <v>5974</v>
+        <v>13925</v>
       </c>
       <c r="AH25" s="2" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
@@ -3501,22 +3493,22 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>64.3</v>
+        <v>91.7</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>83.8</v>
+        <v>75</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>100</v>
@@ -3528,73 +3520,73 @@
         <v>0</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>13.68</v>
+        <v>195.64</v>
       </c>
       <c r="O26" s="2" t="n">
-        <v>12.31</v>
+        <v>165.44</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>1.37</v>
+        <v>30.19</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>147.79</v>
+        <v>780.0599999999999</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>125.62</v>
+        <v>749.67</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>22.17</v>
+        <v>30.39</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>1592</v>
+        <v>2846</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>17114</v>
+        <v>25698</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>0.00239</v>
+        <v>0.0071</v>
       </c>
       <c r="W26" s="2" t="n">
-        <v>0.02867</v>
+        <v>0.0696344</v>
       </c>
       <c r="X26" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Y26" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z26" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA26" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26" s="2" t="n">
-        <v>2.9</v>
+        <v>47.14</v>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE26" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Modelu jest poprawna, ale nie wyjaśnia w pełni dlaczego znane wzorce dla liczb doskonałych są używane. Zamiast tego skupia się na optymalizacji bez szczegółowego uzasadnienia. Odpowiedź Multi-Agent Tura 5 jest niewystarczająca, ponieważ polega wyłącznie na wcześniej znanych wynikach bez wyjaśnienia ich pochodzenia lub poprawności. W Tury 10 i Finałowej Multi-Agent dostarcza kompleksowego uzasadnienia, potwierdzając właściwości liczb doskonałych i poprawność wyniku, co jest zgodne z wzorcem. | [qwen2.5:14b]: Odpowiedź SOLO jest idealna, zgodna z WZORCEM i poprawnie uzasadniona. Odpowiedź MULTI-5 ma poprawny wynik, ale nie wykorzystuje efektywnego algorytmu do znalezienia perfekcyjnych liczb. Odpowiedź MULTI-Final zawiera halucynację (przypuszcza odkrycie nowych perfekcyjnych liczb), co jest niepoprawne. | [mistral-nemo:12b]: Odpowiedź idealna, zgodna z WZORCEM, poprawne uzasadnienie i dowód.</t>
         </is>
       </c>
       <c r="AF26" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Błąd Wykonania Kodu / Narzędzia (Tool Execution Failure)</t>
         </is>
       </c>
       <c r="AG26" s="2" t="n">
-        <v>4444</v>
+        <v>13816</v>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>64</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -3619,22 +3611,22 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>64.3</v>
+        <v>83.3</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>79.7</v>
+        <v>100</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>100</v>
@@ -3646,61 +3638,61 @@
         <v>0</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>10.3</v>
+        <v>39.7</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>9.27</v>
+        <v>39.62</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>1.03</v>
+        <v>0.08</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>111.97</v>
+        <v>334.69</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>95.17</v>
+        <v>334.51</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>16.8</v>
+        <v>0.18</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>2024</v>
+        <v>1842</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>6962</v>
+        <v>20719</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>0.00304</v>
+        <v>0.0046</v>
       </c>
       <c r="W27" s="2" t="n">
-        <v>0.01344</v>
+        <v>0.0541528</v>
       </c>
       <c r="X27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y27" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Y27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB27" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="AC27" s="2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE27" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest zgodna z wynikiem, ale brakuje szczegółowego uzasadnienia i logiki. Odpowiedzi Multi-Agent są kompleksowe, zawierają poprawny kod oraz dokładne wyjaśnienie procesu weryfikacji, co czyni je idealnymi. | [qwen2.5:14b]: Wszystkie odpowiedzi są zgodne z wzorcem, zawierają poprawny kod Pythona i uzasadnienie. Brak halucynacji. | [mistral-nemo:12b]: Odpowiedzi są zgodne z WZORCEM i poprawnie uzasadnione. Wyniki są dokładnie obliczone za pomocą Python i datetime, a także uwzględniają przypadki na krawędziach.</t>
         </is>
       </c>
       <c r="AF27" s="2" t="inlineStr">
@@ -3709,10 +3701,10 @@
         </is>
       </c>
       <c r="AG27" s="2" t="n">
-        <v>4747</v>
+        <v>13815</v>
       </c>
       <c r="AH27" s="2" t="n">
-        <v>77</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -3737,22 +3729,22 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>43.1</v>
+        <v>91.7</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>57.8</v>
+        <v>100</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>31.3</v>
+        <v>0</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>100</v>
@@ -3764,61 +3756,61 @@
         <v>0</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>19.4</v>
+        <v>158.31</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>17.46</v>
+        <v>158.26</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>1.94</v>
+        <v>0.05</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>135.53</v>
+        <v>498.05</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>115.2</v>
+        <v>497.83</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>20.33</v>
+        <v>0.22</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>1956</v>
+        <v>2027</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>10815</v>
+        <v>27754</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>0.00293</v>
+        <v>0.0051</v>
       </c>
       <c r="W28" s="2" t="n">
-        <v>0.01922</v>
+        <v>0.0728138</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y28" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA28" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="Z28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AB28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC28" s="2" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE28" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest idealna, zgodna z WZORCEM i zawiera poprawne uzasadnienie. Odpowiedź Multi-Agent Tura 5 również jest idealna, z poprawnym kodem Python i wynikiem. Tura 10 zawiera nieco błędne obliczenia dla F#4 (377.38 Hz zamiast 369.99 Hz), co wpływa na ocenę. Ostateczna odpowiedź Multi-Agent jest idealna, poprawnie uzasadniona i zgodna z WZORCEM. | [qwen2.5:14b]: Wszystkie odpowiedzi są zgodne z wzorcem i nie zawierają błędów logiki lub halucynacji. | [mistral-nemo:12b]: Odpowiedzi są zgodne z WZORCEM, uzasadnienie jest precyzyjne i poprawne.</t>
         </is>
       </c>
       <c r="AF28" s="2" t="inlineStr">
@@ -3827,10 +3819,10 @@
         </is>
       </c>
       <c r="AG28" s="2" t="n">
-        <v>4872</v>
+        <v>13870</v>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>92</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
@@ -3855,100 +3847,100 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>70.7</v>
+        <v>100</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>77.7</v>
+        <v>91.7</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>85.8</v>
+        <v>25</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>97.2</v>
+        <v>16.7</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>19.5</v>
+        <v>-75</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M29" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>9.49</v>
+        <v>25.21</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>8.539999999999999</v>
+        <v>23.91</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>0.95</v>
+        <v>1.29</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>48.39</v>
+        <v>296.59</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>41.13</v>
+        <v>296.25</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>7.26</v>
+        <v>0.34</v>
       </c>
       <c r="T29" s="2" t="n">
-        <v>1657</v>
+        <v>1648</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>15811</v>
+        <v>22333</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>0.00249</v>
+        <v>0.0041</v>
       </c>
       <c r="W29" s="2" t="n">
-        <v>0.02672</v>
+        <v>0.04960970000000001</v>
       </c>
       <c r="X29" s="2" t="n">
         <v>2</v>
       </c>
       <c r="Y29" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Z29" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA29" s="2" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AB29" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC29" s="2" t="n">
-        <v>2.4</v>
+        <v>11.79</v>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>archivist -&gt; coder -&gt; qa_engineer -&gt; archivist -&gt; coder -&gt; qa_engineer -&gt; archivist -&gt; coder -&gt; qa_engineer -&gt; archivist -&gt; coder -&gt; qa_engineer -&gt; archivist -&gt; secretary</t>
         </is>
       </c>
       <c r="AE29" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest idealna, zgodnie z WZORCEM. Oblicza poprawny Net Profit Margin na podstawie prawidłowych danych (Net Profit = 300000 PLN, Revenue = 1200000 PLN), co prowadzi do wyniku 25.0%. Odpowiedź Multi-Agent Tura 5 jest również idealna z tymi samymi obliczeniami i wynikiem. Jednak w odpowiedzi Multi-Agent Tura 10 użyto niepoprawnych danych (Net Profit = 1200000 PLN, Revenue = 5000000 PLN), co prowadzi do błędnego Net Profit Margin wynoszącego 24.0%. Odpowiedź Multi-Agent Finał kontynuuje ten błąd, używając tych samych niepoprawnych danych i obliczeń, co wskazuje na halucynację lub nieścisłość w odniesieniu do WZORCA. | [qwen2.5:14b]: Odpowiedź SOLO jest idealna, zgodna z wzorcem. Odpowiedź MULTI_10 zawiera błędną logikę i niepoprawne dane, a odpowiedź MULTI_FINAŁ ma błędny wynik i halucynację. | [mistral-nemo:12b]: Odpowiedź Solo Model - ReAct jest zgodna z WZORCEM, ale odpowiedzi Multi-Agent mają błędne dane wejściowe lub niepoprawną logikę. Odpowiedź Multi-Agent - Finał ma błędny wynik, choć uzasadnienie jest poprawne.</t>
         </is>
       </c>
       <c r="AF29" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Błąd Wykonania Kodu / Narzędzia (Tool Execution Failure)</t>
         </is>
       </c>
       <c r="AG29" s="2" t="n">
-        <v>4108</v>
+        <v>13872</v>
       </c>
       <c r="AH29" s="2" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
@@ -3973,67 +3965,67 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>56.6</v>
+        <v>50</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>69.5</v>
+        <v>66.7</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>92.8</v>
+        <v>66.7</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>34.23</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>7.52</v>
+        <v>34.23</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>100.72</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>85.61</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>15.11</v>
+        <v>0</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>1268</v>
+        <v>2283</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>7896</v>
+        <v>8805</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>0.0019</v>
+        <v>0.0057</v>
       </c>
       <c r="W30" s="2" t="n">
-        <v>0.01484</v>
+        <v>0.0231243</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y30" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z30" s="2" t="n">
         <v>1</v>
@@ -4045,28 +4037,28 @@
         <v>0</v>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>2.3</v>
+        <v>47.14</v>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>archivist -&gt; solver -&gt; critic -&gt; secretary</t>
         </is>
       </c>
       <c r="AE30" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model nie spełnia WZORCA, ponieważ zawiera procedurę odtwarzania serwera i instrukcje dotyczące kontaktu z IT Security dla hasła, co jest niezgodne z wymaganym formatem. Odpowiedzi Multi-Agent również nie spełniają WZORCA, ponieważ przedstawiają kompletną procedurę odtwarzania serwera i używają innego haseł do bazy danych niż to określone w WZORCU. | [qwen2.5:14b]: Odpowiedź SOLO jest częściowo poprawna, ale brakuje kroku z procedury awaryjnej odtwarzania serwera. Odpowiedzi MULTI-Agent są idealne i dokładnie przestrzegają wzorca. | [mistral-nemo:12b]: Odpowiedzi są zgodne z WZORCEM, ale w niektórych przypadkach uzasadnienie jest nieco nieścisłe.</t>
         </is>
       </c>
       <c r="AF30" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Kaskada Halucynacji (Cascading Hallucination)</t>
         </is>
       </c>
       <c r="AG30" s="2" t="n">
-        <v>6142</v>
+        <v>13700</v>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
@@ -4091,100 +4083,100 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>73.7</v>
+        <v>41.7</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>88.59999999999999</v>
+        <v>41.7</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>98.2</v>
+        <v>41.7</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>100</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M31" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>7.94</v>
+        <v>15.01</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>7.15</v>
+        <v>15.01</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>157.18</v>
+        <v>57.85</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>133.6</v>
+        <v>57.85</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>23.58</v>
+        <v>0</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>2195</v>
+        <v>1456</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>21714</v>
+        <v>6269</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>0.00329</v>
+        <v>0.0036</v>
       </c>
       <c r="W31" s="2" t="n">
-        <v>0.03557</v>
+        <v>0.0134484</v>
       </c>
       <c r="X31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Y31" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA31" s="2" t="n">
-        <v>3</v>
-      </c>
       <c r="AB31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC31" s="2" t="n">
-        <v>1.3</v>
+        <v>42.49</v>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>archivist -&gt; solver -&gt; critic -&gt; secretary</t>
         </is>
       </c>
       <c r="AE31" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest dokładnie zgodna ze WZORCEM, podając poprawny status operacyjny jako 'Krytyczny', kod autoryzacji dostępu jako 778899 oraz adres IP serwera głównego jako 10.200.45.12. Odpowiedzi Multi-Agent (Tura 5, Tura 10 i Finał) są niepoprawne, ponieważ podają różne wartości niż te określone w WZORCU, co stanowi halucynację. | [qwen2.5:14b]: Wszystkie odpowiedzi zawierają błędy w danych (status operacyjny, kod dostępu i adres IP), co nie jest zgodne z wzorcem. Dodatkowo, odpowiedź A (Solo Model - ReAct) ma różne dane niż pozostałe odpowiedzi, sugerując halucynację. | [mistral-nemo:12b]: Odpowiedź A jest częściowo poprawna, ale zawiera nieścisłości w uzasadnieniu. Odpowiedzi B, C i D są idealne, zgodne z WZORCEM i poprawnie uzasadnione.</t>
         </is>
       </c>
       <c r="AF31" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Kaskada Halucynacji (Cascading Hallucination)</t>
         </is>
       </c>
       <c r="AG31" s="2" t="n">
-        <v>5431</v>
+        <v>13702</v>
       </c>
       <c r="AH31" s="2" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
@@ -4209,100 +4201,100 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>75</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>97.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>100</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="b">
         <v>0</v>
       </c>
       <c r="M32" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>13.55</v>
+        <v>12.86</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>12.2</v>
+        <v>10.51</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>1.35</v>
+        <v>2.35</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>39.85</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>57.46</v>
+        <v>39.85</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>10.14</v>
+        <v>0</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>961</v>
+        <v>503</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>20671</v>
+        <v>4676</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>0.00144</v>
+        <v>0.0013</v>
       </c>
       <c r="W32" s="2" t="n">
-        <v>0.03401</v>
+        <v>0.0114952</v>
       </c>
       <c r="X32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Y32" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AA32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>3.3</v>
+        <v>11.79</v>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>analyst -&gt; solver -&gt; critic -&gt; secretary</t>
         </is>
       </c>
       <c r="AE32" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest dokładna i zgodna ze wzorcem, podając poprawny CVE ID (CVE-2014-0160), rok ujawnienia (2014) oraz nazwę podatnej funkcji (TLS/DTLS Heartbeat extension). Wszystkie odpowiedzi Multi-Agent są niepoprawne z powodu błędnie podanego CVE ID (CVE-2014-0129), co stanowi halucynację, ponieważ nie zgadza się to z uznawanymi informacjami. | [qwen2.5:14b]: Odpowiedź Solo jest prawidłowa, ale ma nieścisłości w uzasadnieniu. Wszystkie odpowiedzi wieloagentowe mają błędy w identyfikatorze CVE i halucynują. | [mistral-nemo:12b]: Odpowiedź Solo Model jest poprawna, ale odpowiedzi Multi-Agent zawierają błędny CVE identifier i są powtórzone w różnych turach. Wyniki nie są zgodne z WZORCEM.</t>
         </is>
       </c>
       <c r="AF32" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Kaskada Halucynacji (Cascading Hallucination)</t>
         </is>
       </c>
       <c r="AG32" s="2" t="n">
-        <v>5534</v>
+        <v>13702</v>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
@@ -4327,25 +4319,25 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>66.8</v>
+        <v>91.7</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>87.7</v>
+        <v>100</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="b">
         <v>1</v>
@@ -4354,73 +4346,73 @@
         <v>0</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>19.38</v>
+        <v>56.04</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>17.44</v>
+        <v>55.98</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>1.94</v>
+        <v>0.06</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>75.78</v>
+        <v>516.17</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>64.41</v>
+        <v>516</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>11.37</v>
+        <v>0.17</v>
       </c>
       <c r="T33" s="2" t="n">
-        <v>1483</v>
+        <v>2375</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>9361</v>
+        <v>29491</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>0.00222</v>
+        <v>0.0059</v>
       </c>
       <c r="W33" s="2" t="n">
-        <v>0.01704</v>
+        <v>0.0758185</v>
       </c>
       <c r="X33" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y33" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA33" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AB33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC33" s="2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE33" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model zawiera błędne wyniki i niepoprawnie interpretuje wyjście, sugerując maksymalną wartość $130 z niewłaściwymi elementami. Odpowiedzi Multi-Agent są poprawne, zgodne z WZORCEM, pokazując maksymalną wartość $120 i poprawne zestawy elementów. | [qwen2.5:14b]: Odpowiedź SOLO zawiera niepoprawne informacje o wadze i wartościach wybranych przedmiotów, co prowadzi do błędnego wyniku. Odpowiedzi MULTI-Agent są poprawne i zgodne z WZORCEM. | [mistral-nemo:12b]: Odpowiedzi są zgodne z WZORCEM, uzasadnienie jest precyzyjne i poprawne.</t>
         </is>
       </c>
       <c r="AF33" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Przekroczenie Limitu Tur (No-Consensus Timeout)</t>
         </is>
       </c>
       <c r="AG33" s="2" t="n">
-        <v>5198</v>
+        <v>13705</v>
       </c>
       <c r="AH33" s="2" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -4445,88 +4437,88 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>63.3</v>
+        <v>33.3</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>67.2</v>
+        <v>66.7</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>87.3</v>
+        <v>96.7</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.3</v>
+        <v>33.3</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>100</v>
       </c>
       <c r="L34" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="b">
         <v>0</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>17.58</v>
+        <v>45.61</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>15.82</v>
+        <v>45.53</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>1.76</v>
+        <v>0.09</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>47.5</v>
+        <v>462.87</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>40.38</v>
+        <v>462.47</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>7.12</v>
+        <v>0.4</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>1418</v>
+        <v>2354</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>16286</v>
+        <v>34502</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>0.00213</v>
+        <v>0.0059</v>
       </c>
       <c r="W34" s="2" t="n">
-        <v>0.02743</v>
+        <v>0.0888644</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y34" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z34" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA34" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE34" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo nie zawierała poprawnego kodu Python ani uzasadnienia, co skutkowało błędnym wynikiem. Odpowiedź Multi-Agent w turze 5 próbowała użyć biblioteki PyJWT, ale nie uwzględniła braku modułu 'jwt', co doprowadziło do błędu wykonania. W turze 10 odpowiedź została poprawiona przez ręczne dekodowanie Base64 i uzyskanie poprawnego wyniku zgodnie z wzorcem, bez halucynacji. | [qwen2.5:14b]: Wersja Solo zawiera halucynację, ponieważ sugeruje, że token został poprawnie zasignowany bez dostępu do klucza tajnego. Wersje Multi-Agent są bardziej realistyczne i uwzględniają brak dostępu do klucz a oraz potencjalne zagrożenia bezpieczeństwa. | [mistral-nemo:12b]: Odpowiedź A jest częściowo poprawna, ale uzasadnienie mało precyzyjne. Odpowiedź B jest poprawna, ale zawiera błąd w kodzie Python. Odpowiedź C jest poprawna i zgodna z WZORCEM. Odpowiedź D jest idealna, zgodna z WZORCEM i poprawnym uzasadnieniem.</t>
         </is>
       </c>
       <c r="AF34" s="2" t="inlineStr">
@@ -4535,10 +4527,10 @@
         </is>
       </c>
       <c r="AG34" s="2" t="n">
-        <v>4959</v>
+        <v>13695</v>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>72</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
@@ -4563,22 +4555,22 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>63.8</v>
+        <v>75</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>100</v>
@@ -4590,61 +4582,61 @@
         <v>0</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>16.28</v>
+        <v>28.27</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>14.65</v>
+        <v>28.17</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>1.63</v>
+        <v>0.1</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>60.02</v>
+        <v>284.4</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>51.02</v>
+        <v>283.98</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>9</v>
+        <v>0.42</v>
       </c>
       <c r="T35" s="2" t="n">
-        <v>1116</v>
+        <v>806</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>19086</v>
+        <v>21015</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>0.00167</v>
+        <v>0.002</v>
       </c>
       <c r="W35" s="2" t="n">
-        <v>0.03163</v>
+        <v>0.0558331</v>
       </c>
       <c r="X35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Y35" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Z35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA35" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AB35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC35" s="2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; qa_engineer -&gt; coder -&gt; secretary</t>
         </is>
       </c>
       <c r="AE35" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model (ReAct) wyprodukowała wynik 3.1425, który jest nieco poza zakresem WZORCA (~3.1416 lub między 3.1380 a 3.1450). Jednakże, użyto poprawnej metody i logiki do oszacowania Pi za pomocą metody Monte Carlo, co uzasadnia punktację 75. Odpowiedzi Multi-Agent (Tura 5, Tura 10, Finał) wyprodukowały spójny wynik 3.1395, który jest w zakresie WZORCA i poprawnie zastosowały metodę Monte Carlo do oszacowania Pi. Dlatego uzyskały pełną punktację 100. | [qwen2.5:14b]: Wynik SOLO jest poprawny, ale nie zawiera pełnego uzasadnienia. Wyniki MULTI-Agent są doskonałe i zgodne z wymaganiami. | [mistral-nemo:12b]: Wyniki poprawne i zgodne z WZORCEM. Uzyskanie dokładnej wartości Pi za pomocą metody Monte Carlo jest zależne od liczby prób, ale wyniki są w przybliżeniu 3.14, co jest oczekiwane.</t>
         </is>
       </c>
       <c r="AF35" s="2" t="inlineStr">
@@ -4653,10 +4645,10 @@
         </is>
       </c>
       <c r="AG35" s="2" t="n">
-        <v>4253</v>
+        <v>13704</v>
       </c>
       <c r="AH35" s="2" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
@@ -4681,26 +4673,26 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>89.3</v>
+        <v>58.3</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>89.2</v>
+        <v>58.3</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="K36" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="K36" s="2" t="n">
-        <v>100</v>
-      </c>
       <c r="L36" s="2" t="b">
         <v>0</v>
       </c>
@@ -4708,73 +4700,73 @@
         <v>0</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>15.51</v>
+        <v>25.37</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>13.96</v>
+        <v>25.31</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>1.55</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>117.47</v>
+        <v>109.66</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>109.44</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>17.62</v>
+        <v>0.22</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>1875</v>
+        <v>771</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>8088</v>
+        <v>9485</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>0.00281</v>
+        <v>0.0019</v>
       </c>
       <c r="W36" s="2" t="n">
-        <v>0.01513</v>
+        <v>0.0234469</v>
       </c>
       <c r="X36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Y36" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Z36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AA36" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC36" s="2" t="n">
-        <v>4.1</v>
+        <v>42.49</v>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>fact_checker -&gt; solver -&gt; devil -&gt; coder -&gt; qa_engineer -&gt; solver -&gt; critic -&gt; secretary</t>
+          <t>security_auditor -&gt; solver -&gt; critic -&gt; secretary</t>
         </is>
       </c>
       <c r="AE36" s="2" t="inlineStr">
         <is>
-          <t>[qwen2.5:14b]: Odpowiedź precyzyjna, zweryfikowana empirycznie przez Coder i skontrowana przez Devil.</t>
+          <t>[phi4:latest]: Odpowiedź Solo Model jest idealna, zgodnie z WZORCEM. Poprawnie identyfikuje podatność na SQL Injection (CWE-89), dostarcza przykładowe ciągi ataków i poprawia kod używając parametryzowanych zapytań. Odpowiedzi Multi-Agent zawierają niepotrzebne kroki, takie jak tworzenie tabeli i wstawianie danych, które są nieistotne dla zadania zapobiegania SQL Injection. Ponadto, powtarzają się błędy związane z naruszeniem ograniczenia UNIQUE, co sugeruje, że te odpowiedzi zawierają halucynacje dotyczące kontekstu i wymagań zadania. | [qwen2.5:14b]: Odpowiedź SOLO jest idealna, zgodna z wzorcem. Odpowiedzi MULTI-Agent są częściowo poprawne, ale zawierają niepotrzebny kod tworzenia tabeli i wstawiania danych, co prowadzi do błędu IntegrityError. | [mistral-nemo:12b]: Odpowiedź zgodna z WZORCEM, poprawne uzasadnienie i dowód.</t>
         </is>
       </c>
       <c r="AF36" s="2" t="inlineStr">
         <is>
-          <t>Brak Błędu (Sukces Merytoryczny)</t>
+          <t>Błąd Wykonania Kodu / Narzędzia (Tool Execution Failure)</t>
         </is>
       </c>
       <c r="AG36" s="2" t="n">
-        <v>4738</v>
+        <v>13704</v>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>66</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -4859,25 +4851,25 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>61.85</v>
+        <v>41.7</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>18.14</v>
+        <v>69.12</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>116.69</v>
+        <v>509.43</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25.65</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="3">
@@ -4890,16 +4882,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>89.2</v>
+        <v>58.3</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>15.51</v>
+        <v>25.37</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>117.47</v>
+        <v>109.66</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
@@ -4908,7 +4900,7 @@
         <v>0.02</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>18.3</v>
+        <v>-41.7</v>
       </c>
     </row>
     <row r="4">
@@ -4921,25 +4913,25 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>69.58</v>
+        <v>64.55</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>90.34999999999999</v>
+        <v>100</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13.08</v>
+        <v>52.07</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>92.45999999999999</v>
+        <v>414.79</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>20.77</v>
+        <v>35.45</v>
       </c>
     </row>
     <row r="5">
@@ -4952,25 +4944,25 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>76.67</v>
+        <v>75</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>95.43000000000001</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>22.08</v>
+        <v>65.81</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>92.81999999999999</v>
+        <v>928.95</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>18.76</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="6">
@@ -4983,25 +4975,25 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>62.23</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>89.81999999999999</v>
+        <v>93.62</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>18.76</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>111.98</v>
+        <v>410.52</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>27.59</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -5014,25 +5006,25 @@
         <v>3</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>71.87</v>
+        <v>61.1</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>92.87</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14.51</v>
+        <v>34.77</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>73.83</v>
+        <v>591.61</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>21</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="8">
@@ -5045,25 +5037,25 @@
         <v>3</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>65.03</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>89.53</v>
+        <v>87.23</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>10.39</v>
+        <v>28.28</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>101.64</v>
+        <v>273.03</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>24.5</v>
+        <v>16.13</v>
       </c>
     </row>
     <row r="9">
@@ -5076,25 +5068,25 @@
         <v>3</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>77.93000000000001</v>
+        <v>50</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>94.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12.34</v>
+        <v>21.91</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>108.77</v>
+        <v>269.26</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -5107,16 +5099,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>74.8</v>
+        <v>41.7</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>19.76</v>
+        <v>25.72</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>62.8</v>
+        <v>296.91</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0</v>
@@ -5125,7 +5117,7 @@
         <v>0.03</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>20</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="11">
@@ -5138,16 +5130,16 @@
         <v>3</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>71.13</v>
+        <v>69.43000000000001</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>96.06999999999999</v>
+        <v>41.7</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8.6</v>
+        <v>24.82</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>102.1</v>
+        <v>148.22</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0</v>
@@ -5156,7 +5148,7 @@
         <v>0.03</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>24.94</v>
+        <v>-27.73</v>
       </c>
     </row>
     <row r="12">
@@ -5169,25 +5161,25 @@
         <v>4</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>64.62</v>
+        <v>56.22</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>89.2</v>
+        <v>97.92</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>20.19</v>
+        <v>32.64</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>104.71</v>
+        <v>413.26</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>24.58</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="13">
@@ -5200,25 +5192,25 @@
         <v>2</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>85.25</v>
+        <v>83.3</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>96.2</v>
+        <v>20.8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17.16</v>
+        <v>19.45</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>69.59999999999999</v>
+        <v>43.82</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10.95</v>
+        <v>-62.5</v>
       </c>
     </row>
   </sheetData>
@@ -5303,25 +5295,25 @@
         <v>10</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>83.84999999999999</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>96</v>
+        <v>68.33</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14.98</v>
+        <v>26.48</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>93.09</v>
+        <v>255.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1499.9</v>
+        <v>1315.3</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>14884.8</v>
+        <v>16802.2</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>12.15</v>
+        <v>-4.99</v>
       </c>
     </row>
     <row r="3">
@@ -5334,25 +5326,25 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>60.45</v>
+        <v>58.34</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>87.2</v>
+        <v>88.55</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17.38</v>
+        <v>89.52</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>121.33</v>
+        <v>545.42</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1647.62</v>
+        <v>2081.25</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>14596.25</v>
+        <v>27004.38</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>26.75</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="4">
@@ -5365,25 +5357,25 @@
         <v>17</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>65.64</v>
+        <v>68.72</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>91.52</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15.67</v>
+        <v>33.93</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>91.14</v>
+        <v>411.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1510.06</v>
+        <v>1179.29</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>13853.88</v>
+        <v>21941.24</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>25.88</v>
+        <v>20.21</v>
       </c>
     </row>
   </sheetData>
@@ -5447,19 +5439,19 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>77.5</v>
+        <v>100</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -5469,19 +5461,19 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>88.7</v>
+        <v>95</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>23.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -5491,19 +5483,19 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>63.5</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>73.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>81.5</v>
+        <v>85</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -5513,19 +5505,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>55.2</v>
+        <v>75</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>82.8</v>
+        <v>98.3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>88.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5535,19 +5527,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>87.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>89.8</v>
+        <v>98.3</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>15.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5557,19 +5549,19 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>67</v>
+        <v>33.3</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>78.3</v>
+        <v>83.3</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>83.2</v>
+        <v>86.7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>88.8</v>
+        <v>91.7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="8">
@@ -5579,19 +5571,19 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>85.2</v>
+        <v>66.7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>82.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>13.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -5601,19 +5593,19 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>65.3</v>
+        <v>58.3</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>64.59999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>75.8</v>
+        <v>58.3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>85.5</v>
+        <v>66.7</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>20.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="10">
@@ -5623,19 +5615,19 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>74.8</v>
+        <v>41.7</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>68.7</v>
+        <v>83.3</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>85.5</v>
+        <v>83.3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>94.8</v>
+        <v>100</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>26.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="11">
@@ -5645,19 +5637,19 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>89.40000000000001</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>72</v>
+        <v>33.3</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>87.2</v>
+        <v>33.3</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>95.90000000000001</v>
+        <v>33.3</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>23.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5667,19 +5659,19 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>75.2</v>
+        <v>83.3</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>72.8</v>
+        <v>91.7</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>80.40000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>85.2</v>
+        <v>100</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>12.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -5689,19 +5681,19 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>62.6</v>
+        <v>83.3</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>79.5</v>
+        <v>100</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>27.4</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="14">
@@ -5711,19 +5703,19 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>59.9</v>
+        <v>100</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>78.8</v>
+        <v>100</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>78.5</v>
+        <v>100</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -5733,19 +5725,19 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>71.5</v>
+        <v>41.7</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>67.8</v>
+        <v>33.3</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>81.3</v>
+        <v>41.7</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>24.1</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="16">
@@ -5755,19 +5747,19 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>85.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>76.7</v>
+        <v>33.3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>90.3</v>
+        <v>33.3</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>95.2</v>
+        <v>33.3</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5777,19 +5769,19 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>82</v>
+        <v>83.3</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>90.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>95.7</v>
+        <v>66.7</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>23.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="18">
@@ -5799,19 +5791,19 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>57.4</v>
+        <v>25</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>71.5</v>
+        <v>91.7</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>79.3</v>
+        <v>91.7</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>85.8</v>
+        <v>91.7</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5821,19 +5813,19 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>75.3</v>
+        <v>83.3</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>94</v>
+        <v>98.3</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>92.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5843,19 +5835,19 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>58.8</v>
+        <v>41.7</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>69.3</v>
+        <v>91.7</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>75.5</v>
+        <v>98.3</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>87.3</v>
+        <v>100</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>18</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -5865,19 +5857,19 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>62.1</v>
+        <v>58.3</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>63.7</v>
+        <v>91.7</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>75.3</v>
+        <v>80</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>27.3</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="22">
@@ -5887,19 +5879,19 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>76.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>24.3</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="23">
@@ -5909,19 +5901,19 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>59.6</v>
+        <v>75</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>86.59999999999999</v>
+        <v>61.7</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>92</v>
+        <v>96.7</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>26.6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -5931,19 +5923,19 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>68.8</v>
+        <v>83.3</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>74.8</v>
+        <v>100</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>89.5</v>
+        <v>100</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>16.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -5953,19 +5945,19 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>85.2</v>
+        <v>83.3</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>72.3</v>
+        <v>91.7</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>92.5</v>
+        <v>98.3</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>98.7</v>
+        <v>100</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>26.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -5975,19 +5967,19 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>64.3</v>
+        <v>91.7</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>83.8</v>
+        <v>75</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -5997,19 +5989,19 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>64.3</v>
+        <v>83.3</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>79.7</v>
+        <v>100</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -6019,19 +6011,19 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>43.1</v>
+        <v>91.7</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>57.8</v>
+        <v>100</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>31.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -6041,19 +6033,19 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>70.7</v>
+        <v>100</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>77.7</v>
+        <v>91.7</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>85.8</v>
+        <v>25</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>97.2</v>
+        <v>16.7</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>19.5</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30">
@@ -6063,19 +6055,19 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>56.6</v>
+        <v>50</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>69.5</v>
+        <v>66.7</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>84.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>92.8</v>
+        <v>66.7</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -6085,19 +6077,19 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>73.7</v>
+        <v>41.7</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>88.59999999999999</v>
+        <v>41.7</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>98.2</v>
+        <v>41.7</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>24.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -6107,19 +6099,19 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>85.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>75</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>97.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -6129,19 +6121,19 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>66.8</v>
+        <v>91.7</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>87.7</v>
+        <v>100</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>20.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -6151,19 +6143,19 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>63.3</v>
+        <v>33.3</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>67.2</v>
+        <v>66.7</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>87.3</v>
+        <v>96.7</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>21.3</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="35">
@@ -6173,19 +6165,19 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>63.8</v>
+        <v>75</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -6195,19 +6187,19 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>74.90000000000001</v>
+        <v>58.3</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>89.3</v>
+        <v>58.3</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>89.2</v>
+        <v>58.3</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6257,7 +6249,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>69.66</v>
+        <v>67.66</v>
       </c>
     </row>
     <row r="4">
@@ -6267,7 +6259,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>10.88</v>
+        <v>24.14</v>
       </c>
     </row>
     <row r="5">
@@ -6277,7 +6269,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
@@ -6287,7 +6279,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>91.81</v>
+        <v>82.95999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -6297,7 +6289,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.27</v>
+        <v>26.44</v>
       </c>
     </row>
     <row r="8">
@@ -6307,7 +6299,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -6317,7 +6309,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>22.16</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="10">
@@ -6327,7 +6319,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>2.342</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="11">
@@ -6337,7 +6329,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -6347,7 +6339,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6357,7 +6349,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -6367,7 +6359,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>100</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -6377,7 +6369,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0</v>
+        <v>0.02484</v>
       </c>
     </row>
     <row r="16">
@@ -6397,7 +6389,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0</v>
+        <v>0.009690000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -6417,7 +6409,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2.49</v>
+        <v>13.14</v>
       </c>
     </row>
   </sheetData>
